--- a/output/version3/test/20-15/MARL/IL/RL-RL (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-15/MARL/IL/RL-RL (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
+        <v>884</v>
+      </c>
+      <c r="C2" t="n">
+        <v>814</v>
+      </c>
+      <c r="D2" t="n">
+        <v>932</v>
+      </c>
+      <c r="E2" t="n">
+        <v>949</v>
+      </c>
+      <c r="F2" t="n">
+        <v>924</v>
+      </c>
+      <c r="G2" t="n">
+        <v>862</v>
+      </c>
+      <c r="H2" t="n">
+        <v>929</v>
+      </c>
+      <c r="I2" t="n">
         <v>1052</v>
       </c>
-      <c r="C2" t="n">
-        <v>892</v>
-      </c>
-      <c r="D2" t="n">
-        <v>751</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1027</v>
-      </c>
-      <c r="F2" t="n">
-        <v>859</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1033</v>
-      </c>
-      <c r="H2" t="n">
-        <v>859</v>
-      </c>
-      <c r="I2" t="n">
-        <v>770</v>
-      </c>
       <c r="J2" t="n">
-        <v>833</v>
+        <v>970</v>
       </c>
       <c r="K2" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="L2" t="n">
-        <v>905.6</v>
+        <v>926.5</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>781</v>
+        <v>947</v>
       </c>
       <c r="C3" t="n">
-        <v>920</v>
+        <v>907</v>
       </c>
       <c r="D3" t="n">
-        <v>958</v>
+        <v>842</v>
       </c>
       <c r="E3" t="n">
-        <v>924</v>
+        <v>877</v>
       </c>
       <c r="F3" t="n">
-        <v>938</v>
+        <v>840</v>
       </c>
       <c r="G3" t="n">
-        <v>1022</v>
+        <v>1063</v>
       </c>
       <c r="H3" t="n">
-        <v>776</v>
+        <v>814</v>
       </c>
       <c r="I3" t="n">
-        <v>1023</v>
+        <v>873</v>
       </c>
       <c r="J3" t="n">
-        <v>1099</v>
+        <v>1080</v>
       </c>
       <c r="K3" t="n">
-        <v>918</v>
+        <v>936</v>
       </c>
       <c r="L3" t="n">
-        <v>935.9</v>
+        <v>917.9</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>817</v>
+        <v>879</v>
       </c>
       <c r="C4" t="n">
-        <v>742</v>
+        <v>823</v>
       </c>
       <c r="D4" t="n">
-        <v>810</v>
+        <v>849</v>
       </c>
       <c r="E4" t="n">
-        <v>896</v>
+        <v>936</v>
       </c>
       <c r="F4" t="n">
-        <v>784</v>
+        <v>821</v>
       </c>
       <c r="G4" t="n">
-        <v>865</v>
+        <v>954</v>
       </c>
       <c r="H4" t="n">
-        <v>910</v>
+        <v>862</v>
       </c>
       <c r="I4" t="n">
-        <v>693</v>
+        <v>988</v>
       </c>
       <c r="J4" t="n">
-        <v>942</v>
+        <v>812</v>
       </c>
       <c r="K4" t="n">
-        <v>991</v>
+        <v>792</v>
       </c>
       <c r="L4" t="n">
-        <v>845</v>
+        <v>871.6</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>975</v>
+        <v>946</v>
       </c>
       <c r="C5" t="n">
-        <v>789</v>
+        <v>830</v>
       </c>
       <c r="D5" t="n">
-        <v>758</v>
+        <v>889</v>
       </c>
       <c r="E5" t="n">
-        <v>977</v>
+        <v>739</v>
       </c>
       <c r="F5" t="n">
-        <v>830</v>
+        <v>1026</v>
       </c>
       <c r="G5" t="n">
-        <v>986</v>
+        <v>715</v>
       </c>
       <c r="H5" t="n">
-        <v>990</v>
+        <v>825</v>
       </c>
       <c r="I5" t="n">
-        <v>777</v>
+        <v>1022</v>
       </c>
       <c r="J5" t="n">
-        <v>796</v>
+        <v>958</v>
       </c>
       <c r="K5" t="n">
-        <v>908</v>
+        <v>1048</v>
       </c>
       <c r="L5" t="n">
-        <v>878.6</v>
+        <v>899.8</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>723</v>
+        <v>784</v>
       </c>
       <c r="C6" t="n">
-        <v>885</v>
+        <v>732</v>
       </c>
       <c r="D6" t="n">
-        <v>692</v>
+        <v>736</v>
       </c>
       <c r="E6" t="n">
-        <v>763</v>
+        <v>797</v>
       </c>
       <c r="F6" t="n">
-        <v>687</v>
+        <v>924</v>
       </c>
       <c r="G6" t="n">
-        <v>668</v>
+        <v>746</v>
       </c>
       <c r="H6" t="n">
-        <v>745</v>
+        <v>715</v>
       </c>
       <c r="I6" t="n">
-        <v>767</v>
+        <v>846</v>
       </c>
       <c r="J6" t="n">
-        <v>748</v>
+        <v>700</v>
       </c>
       <c r="K6" t="n">
-        <v>738</v>
+        <v>859</v>
       </c>
       <c r="L6" t="n">
-        <v>741.6</v>
+        <v>783.9</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>762</v>
+        <v>925</v>
       </c>
       <c r="C7" t="n">
-        <v>794</v>
+        <v>815</v>
       </c>
       <c r="D7" t="n">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="E7" t="n">
-        <v>975</v>
+        <v>804</v>
       </c>
       <c r="F7" t="n">
-        <v>870</v>
+        <v>855</v>
       </c>
       <c r="G7" t="n">
-        <v>874</v>
+        <v>1091</v>
       </c>
       <c r="H7" t="n">
-        <v>802</v>
+        <v>826</v>
       </c>
       <c r="I7" t="n">
-        <v>885</v>
+        <v>826</v>
       </c>
       <c r="J7" t="n">
-        <v>861</v>
+        <v>788</v>
       </c>
       <c r="K7" t="n">
-        <v>916</v>
+        <v>987</v>
       </c>
       <c r="L7" t="n">
-        <v>854.4</v>
+        <v>870.8</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>987</v>
+        <v>796</v>
       </c>
       <c r="C8" t="n">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="D8" t="n">
-        <v>810</v>
+        <v>895</v>
       </c>
       <c r="E8" t="n">
-        <v>939</v>
+        <v>962</v>
       </c>
       <c r="F8" t="n">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="G8" t="n">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="H8" t="n">
-        <v>1032</v>
+        <v>822</v>
       </c>
       <c r="I8" t="n">
-        <v>804</v>
+        <v>985</v>
       </c>
       <c r="J8" t="n">
-        <v>901</v>
+        <v>811</v>
       </c>
       <c r="K8" t="n">
-        <v>931</v>
+        <v>1019</v>
       </c>
       <c r="L8" t="n">
-        <v>890.1</v>
+        <v>879.2</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>931</v>
+        <v>915</v>
       </c>
       <c r="C9" t="n">
-        <v>947</v>
+        <v>920</v>
       </c>
       <c r="D9" t="n">
-        <v>729</v>
+        <v>808</v>
       </c>
       <c r="E9" t="n">
-        <v>740</v>
+        <v>818</v>
       </c>
       <c r="F9" t="n">
-        <v>904</v>
+        <v>850</v>
       </c>
       <c r="G9" t="n">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="H9" t="n">
-        <v>780</v>
+        <v>726</v>
       </c>
       <c r="I9" t="n">
-        <v>846</v>
+        <v>815</v>
       </c>
       <c r="J9" t="n">
-        <v>819</v>
+        <v>1011</v>
       </c>
       <c r="K9" t="n">
-        <v>927</v>
+        <v>943</v>
       </c>
       <c r="L9" t="n">
-        <v>841.4</v>
+        <v>859.4</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>721</v>
+        <v>775</v>
       </c>
       <c r="C10" t="n">
-        <v>799</v>
+        <v>869</v>
       </c>
       <c r="D10" t="n">
-        <v>927</v>
+        <v>876</v>
       </c>
       <c r="E10" t="n">
-        <v>824</v>
+        <v>755</v>
       </c>
       <c r="F10" t="n">
-        <v>790</v>
+        <v>702</v>
       </c>
       <c r="G10" t="n">
-        <v>869</v>
+        <v>740</v>
       </c>
       <c r="H10" t="n">
-        <v>724</v>
+        <v>826</v>
       </c>
       <c r="I10" t="n">
-        <v>747</v>
+        <v>1047</v>
       </c>
       <c r="J10" t="n">
-        <v>708</v>
+        <v>788</v>
       </c>
       <c r="K10" t="n">
-        <v>853</v>
+        <v>910</v>
       </c>
       <c r="L10" t="n">
-        <v>796.2</v>
+        <v>828.8</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C11" t="n">
-        <v>911</v>
+        <v>760</v>
       </c>
       <c r="D11" t="n">
-        <v>1045</v>
+        <v>861</v>
       </c>
       <c r="E11" t="n">
-        <v>902</v>
+        <v>742</v>
       </c>
       <c r="F11" t="n">
-        <v>981</v>
+        <v>901</v>
       </c>
       <c r="G11" t="n">
-        <v>852</v>
+        <v>800</v>
       </c>
       <c r="H11" t="n">
-        <v>748</v>
+        <v>806</v>
       </c>
       <c r="I11" t="n">
-        <v>961</v>
+        <v>1006</v>
       </c>
       <c r="J11" t="n">
-        <v>944</v>
+        <v>983</v>
       </c>
       <c r="K11" t="n">
-        <v>993</v>
+        <v>930</v>
       </c>
       <c r="L11" t="n">
-        <v>919.9</v>
+        <v>865.3</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>963</v>
+        <v>849</v>
       </c>
       <c r="C12" t="n">
-        <v>987</v>
+        <v>959</v>
       </c>
       <c r="D12" t="n">
-        <v>894</v>
+        <v>936</v>
       </c>
       <c r="E12" t="n">
-        <v>1036</v>
+        <v>1078</v>
       </c>
       <c r="F12" t="n">
-        <v>939</v>
+        <v>851</v>
       </c>
       <c r="G12" t="n">
-        <v>1050</v>
+        <v>966</v>
       </c>
       <c r="H12" t="n">
-        <v>1091</v>
+        <v>1047</v>
       </c>
       <c r="I12" t="n">
-        <v>1091</v>
+        <v>851</v>
       </c>
       <c r="J12" t="n">
-        <v>1033</v>
+        <v>986</v>
       </c>
       <c r="K12" t="n">
-        <v>1100</v>
+        <v>898</v>
       </c>
       <c r="L12" t="n">
-        <v>1018.4</v>
+        <v>942.1</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>702</v>
+        <v>814</v>
       </c>
       <c r="C13" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="D13" t="n">
-        <v>853</v>
+        <v>719</v>
       </c>
       <c r="E13" t="n">
-        <v>764</v>
+        <v>857</v>
       </c>
       <c r="F13" t="n">
-        <v>841</v>
+        <v>789</v>
       </c>
       <c r="G13" t="n">
-        <v>816</v>
+        <v>868</v>
       </c>
       <c r="H13" t="n">
-        <v>765</v>
+        <v>733</v>
       </c>
       <c r="I13" t="n">
-        <v>863</v>
+        <v>937</v>
       </c>
       <c r="J13" t="n">
-        <v>788</v>
+        <v>830</v>
       </c>
       <c r="K13" t="n">
-        <v>837</v>
+        <v>821</v>
       </c>
       <c r="L13" t="n">
-        <v>804.9</v>
+        <v>819.2</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>837</v>
+        <v>851</v>
       </c>
       <c r="C14" t="n">
-        <v>791</v>
+        <v>752</v>
       </c>
       <c r="D14" t="n">
-        <v>956</v>
+        <v>878</v>
       </c>
       <c r="E14" t="n">
-        <v>747</v>
+        <v>723</v>
       </c>
       <c r="F14" t="n">
-        <v>750</v>
+        <v>898</v>
       </c>
       <c r="G14" t="n">
-        <v>967</v>
+        <v>795</v>
       </c>
       <c r="H14" t="n">
-        <v>1013</v>
+        <v>801</v>
       </c>
       <c r="I14" t="n">
-        <v>939</v>
+        <v>813</v>
       </c>
       <c r="J14" t="n">
-        <v>927</v>
+        <v>803</v>
       </c>
       <c r="K14" t="n">
-        <v>894</v>
+        <v>1079</v>
       </c>
       <c r="L14" t="n">
-        <v>882.1</v>
+        <v>839.3</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1010</v>
+        <v>827</v>
       </c>
       <c r="C15" t="n">
-        <v>931</v>
+        <v>726</v>
       </c>
       <c r="D15" t="n">
-        <v>981</v>
+        <v>1004</v>
       </c>
       <c r="E15" t="n">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="F15" t="n">
-        <v>856</v>
+        <v>745</v>
       </c>
       <c r="G15" t="n">
-        <v>866</v>
+        <v>912</v>
       </c>
       <c r="H15" t="n">
-        <v>902</v>
+        <v>979</v>
       </c>
       <c r="I15" t="n">
-        <v>878</v>
+        <v>795</v>
       </c>
       <c r="J15" t="n">
-        <v>935</v>
+        <v>827</v>
       </c>
       <c r="K15" t="n">
-        <v>969</v>
+        <v>742</v>
       </c>
       <c r="L15" t="n">
-        <v>913.2</v>
+        <v>836.9</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>929</v>
+        <v>844</v>
       </c>
       <c r="C16" t="n">
-        <v>815</v>
+        <v>748</v>
       </c>
       <c r="D16" t="n">
-        <v>788</v>
+        <v>804</v>
       </c>
       <c r="E16" t="n">
-        <v>857</v>
+        <v>1131</v>
       </c>
       <c r="F16" t="n">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="G16" t="n">
-        <v>1072</v>
+        <v>966</v>
       </c>
       <c r="H16" t="n">
-        <v>791</v>
+        <v>875</v>
       </c>
       <c r="I16" t="n">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="J16" t="n">
-        <v>739</v>
+        <v>818</v>
       </c>
       <c r="K16" t="n">
-        <v>940</v>
+        <v>1030</v>
       </c>
       <c r="L16" t="n">
-        <v>876.5</v>
+        <v>903.5</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>762</v>
+        <v>914</v>
       </c>
       <c r="C17" t="n">
-        <v>790</v>
+        <v>1049</v>
       </c>
       <c r="D17" t="n">
-        <v>950</v>
+        <v>959</v>
       </c>
       <c r="E17" t="n">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="F17" t="n">
-        <v>956</v>
+        <v>880</v>
       </c>
       <c r="G17" t="n">
-        <v>880</v>
+        <v>939</v>
       </c>
       <c r="H17" t="n">
-        <v>822</v>
+        <v>1115</v>
       </c>
       <c r="I17" t="n">
-        <v>856</v>
+        <v>779</v>
       </c>
       <c r="J17" t="n">
-        <v>760</v>
+        <v>872</v>
       </c>
       <c r="K17" t="n">
-        <v>1070</v>
+        <v>743</v>
       </c>
       <c r="L17" t="n">
-        <v>884.3</v>
+        <v>925</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>758</v>
+        <v>902</v>
       </c>
       <c r="C18" t="n">
-        <v>932</v>
+        <v>801</v>
       </c>
       <c r="D18" t="n">
-        <v>862</v>
+        <v>1168</v>
       </c>
       <c r="E18" t="n">
-        <v>853</v>
+        <v>779</v>
       </c>
       <c r="F18" t="n">
-        <v>805</v>
+        <v>774</v>
       </c>
       <c r="G18" t="n">
-        <v>991</v>
+        <v>1005</v>
       </c>
       <c r="H18" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="I18" t="n">
-        <v>1010</v>
+        <v>955</v>
       </c>
       <c r="J18" t="n">
-        <v>1085</v>
+        <v>784</v>
       </c>
       <c r="K18" t="n">
-        <v>883</v>
+        <v>770</v>
       </c>
       <c r="L18" t="n">
-        <v>901.6</v>
+        <v>877.6</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>878</v>
+        <v>860</v>
       </c>
       <c r="C19" t="n">
-        <v>980</v>
+        <v>856</v>
       </c>
       <c r="D19" t="n">
-        <v>752</v>
+        <v>769</v>
       </c>
       <c r="E19" t="n">
-        <v>827</v>
+        <v>901</v>
       </c>
       <c r="F19" t="n">
-        <v>788</v>
+        <v>894</v>
       </c>
       <c r="G19" t="n">
-        <v>895</v>
+        <v>1013</v>
       </c>
       <c r="H19" t="n">
-        <v>757</v>
+        <v>904</v>
       </c>
       <c r="I19" t="n">
-        <v>899</v>
+        <v>963</v>
       </c>
       <c r="J19" t="n">
-        <v>741</v>
+        <v>851</v>
       </c>
       <c r="K19" t="n">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="L19" t="n">
-        <v>843.3</v>
+        <v>893.2</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>840</v>
+        <v>1054</v>
       </c>
       <c r="C20" t="n">
-        <v>862</v>
+        <v>951</v>
       </c>
       <c r="D20" t="n">
-        <v>1055</v>
+        <v>1003</v>
       </c>
       <c r="E20" t="n">
-        <v>1061</v>
+        <v>827</v>
       </c>
       <c r="F20" t="n">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="G20" t="n">
-        <v>837</v>
+        <v>926</v>
       </c>
       <c r="H20" t="n">
-        <v>1003</v>
+        <v>1062</v>
       </c>
       <c r="I20" t="n">
-        <v>814</v>
+        <v>904</v>
       </c>
       <c r="J20" t="n">
-        <v>840</v>
+        <v>853</v>
       </c>
       <c r="K20" t="n">
-        <v>1130</v>
+        <v>835</v>
       </c>
       <c r="L20" t="n">
-        <v>934</v>
+        <v>932.3</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>845</v>
+        <v>935</v>
       </c>
       <c r="C21" t="n">
+        <v>697</v>
+      </c>
+      <c r="D21" t="n">
+        <v>880</v>
+      </c>
+      <c r="E21" t="n">
+        <v>865</v>
+      </c>
+      <c r="F21" t="n">
         <v>971</v>
       </c>
-      <c r="D21" t="n">
-        <v>989</v>
-      </c>
-      <c r="E21" t="n">
-        <v>744</v>
-      </c>
-      <c r="F21" t="n">
-        <v>802</v>
-      </c>
       <c r="G21" t="n">
-        <v>907</v>
+        <v>1084</v>
       </c>
       <c r="H21" t="n">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="I21" t="n">
-        <v>991</v>
+        <v>758</v>
       </c>
       <c r="J21" t="n">
-        <v>744</v>
+        <v>899</v>
       </c>
       <c r="K21" t="n">
-        <v>749</v>
+        <v>850</v>
       </c>
       <c r="L21" t="n">
-        <v>862.8</v>
+        <v>882</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="C22" t="n">
-        <v>798</v>
+        <v>838</v>
       </c>
       <c r="D22" t="n">
-        <v>924</v>
+        <v>957</v>
       </c>
       <c r="E22" t="n">
-        <v>946</v>
+        <v>854</v>
       </c>
       <c r="F22" t="n">
-        <v>1005</v>
+        <v>914</v>
       </c>
       <c r="G22" t="n">
-        <v>1019</v>
+        <v>871</v>
       </c>
       <c r="H22" t="n">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="I22" t="n">
-        <v>854</v>
+        <v>765</v>
       </c>
       <c r="J22" t="n">
-        <v>1067</v>
+        <v>902</v>
       </c>
       <c r="K22" t="n">
-        <v>956</v>
+        <v>799</v>
       </c>
       <c r="L22" t="n">
-        <v>920.7</v>
+        <v>853.5</v>
       </c>
     </row>
     <row r="23">
@@ -1272,34 +1272,34 @@
         <v>1061</v>
       </c>
       <c r="C23" t="n">
-        <v>975</v>
+        <v>853</v>
       </c>
       <c r="D23" t="n">
-        <v>889</v>
+        <v>1001</v>
       </c>
       <c r="E23" t="n">
-        <v>1024</v>
+        <v>1061</v>
       </c>
       <c r="F23" t="n">
-        <v>979</v>
+        <v>1084</v>
       </c>
       <c r="G23" t="n">
-        <v>1040</v>
+        <v>1119</v>
       </c>
       <c r="H23" t="n">
-        <v>848</v>
+        <v>1002</v>
       </c>
       <c r="I23" t="n">
-        <v>931</v>
+        <v>1152</v>
       </c>
       <c r="J23" t="n">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="K23" t="n">
-        <v>978</v>
+        <v>903</v>
       </c>
       <c r="L23" t="n">
-        <v>988.2</v>
+        <v>1038.8</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>932</v>
+        <v>850</v>
       </c>
       <c r="C24" t="n">
-        <v>947</v>
+        <v>938</v>
       </c>
       <c r="D24" t="n">
-        <v>917</v>
+        <v>958</v>
       </c>
       <c r="E24" t="n">
-        <v>915</v>
+        <v>926</v>
       </c>
       <c r="F24" t="n">
-        <v>878</v>
+        <v>1020</v>
       </c>
       <c r="G24" t="n">
-        <v>931</v>
+        <v>920</v>
       </c>
       <c r="H24" t="n">
-        <v>844</v>
+        <v>883</v>
       </c>
       <c r="I24" t="n">
-        <v>934</v>
+        <v>788</v>
       </c>
       <c r="J24" t="n">
-        <v>937</v>
+        <v>969</v>
       </c>
       <c r="K24" t="n">
-        <v>772</v>
+        <v>834</v>
       </c>
       <c r="L24" t="n">
-        <v>900.7</v>
+        <v>908.6</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>978</v>
+        <v>880</v>
       </c>
       <c r="C25" t="n">
-        <v>848</v>
+        <v>990</v>
       </c>
       <c r="D25" t="n">
-        <v>835</v>
+        <v>757</v>
       </c>
       <c r="E25" t="n">
-        <v>799</v>
+        <v>770</v>
       </c>
       <c r="F25" t="n">
-        <v>834</v>
+        <v>995</v>
       </c>
       <c r="G25" t="n">
-        <v>914</v>
+        <v>857</v>
       </c>
       <c r="H25" t="n">
-        <v>849</v>
+        <v>752</v>
       </c>
       <c r="I25" t="n">
-        <v>923</v>
+        <v>956</v>
       </c>
       <c r="J25" t="n">
-        <v>822</v>
+        <v>943</v>
       </c>
       <c r="K25" t="n">
-        <v>1041</v>
+        <v>884</v>
       </c>
       <c r="L25" t="n">
-        <v>884.3</v>
+        <v>878.4</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>740</v>
+        <v>856</v>
       </c>
       <c r="C26" t="n">
-        <v>775</v>
+        <v>920</v>
       </c>
       <c r="D26" t="n">
-        <v>1016</v>
+        <v>784</v>
       </c>
       <c r="E26" t="n">
-        <v>752</v>
+        <v>1064</v>
       </c>
       <c r="F26" t="n">
-        <v>861</v>
+        <v>782</v>
       </c>
       <c r="G26" t="n">
-        <v>811</v>
+        <v>844</v>
       </c>
       <c r="H26" t="n">
-        <v>896</v>
+        <v>934</v>
       </c>
       <c r="I26" t="n">
-        <v>1021</v>
+        <v>851</v>
       </c>
       <c r="J26" t="n">
-        <v>964</v>
+        <v>722</v>
       </c>
       <c r="K26" t="n">
-        <v>745</v>
+        <v>1036</v>
       </c>
       <c r="L26" t="n">
-        <v>858.1</v>
+        <v>879.3</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1000</v>
+        <v>917</v>
       </c>
       <c r="C27" t="n">
-        <v>897</v>
+        <v>1042</v>
       </c>
       <c r="D27" t="n">
-        <v>1103</v>
+        <v>797</v>
       </c>
       <c r="E27" t="n">
-        <v>1053</v>
+        <v>1111</v>
       </c>
       <c r="F27" t="n">
-        <v>1042</v>
+        <v>952</v>
       </c>
       <c r="G27" t="n">
-        <v>1070</v>
+        <v>1043</v>
       </c>
       <c r="H27" t="n">
-        <v>1094</v>
+        <v>993</v>
       </c>
       <c r="I27" t="n">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="J27" t="n">
-        <v>958</v>
+        <v>818</v>
       </c>
       <c r="K27" t="n">
-        <v>1015</v>
+        <v>886</v>
       </c>
       <c r="L27" t="n">
-        <v>1022.8</v>
+        <v>955.1</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>785</v>
+        <v>887</v>
       </c>
       <c r="C28" t="n">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="D28" t="n">
-        <v>970</v>
+        <v>1031</v>
       </c>
       <c r="E28" t="n">
-        <v>960</v>
+        <v>997</v>
       </c>
       <c r="F28" t="n">
-        <v>807</v>
+        <v>995</v>
       </c>
       <c r="G28" t="n">
-        <v>819</v>
+        <v>853</v>
       </c>
       <c r="H28" t="n">
-        <v>1058</v>
+        <v>1025</v>
       </c>
       <c r="I28" t="n">
-        <v>825</v>
+        <v>805</v>
       </c>
       <c r="J28" t="n">
-        <v>770</v>
+        <v>957</v>
       </c>
       <c r="K28" t="n">
-        <v>921</v>
+        <v>900</v>
       </c>
       <c r="L28" t="n">
-        <v>876.4</v>
+        <v>929</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
+        <v>978</v>
+      </c>
+      <c r="C29" t="n">
+        <v>974</v>
+      </c>
+      <c r="D29" t="n">
+        <v>966</v>
+      </c>
+      <c r="E29" t="n">
+        <v>799</v>
+      </c>
+      <c r="F29" t="n">
+        <v>901</v>
+      </c>
+      <c r="G29" t="n">
+        <v>763</v>
+      </c>
+      <c r="H29" t="n">
+        <v>905</v>
+      </c>
+      <c r="I29" t="n">
         <v>903</v>
       </c>
-      <c r="C29" t="n">
-        <v>961</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1077</v>
-      </c>
-      <c r="E29" t="n">
-        <v>897</v>
-      </c>
-      <c r="F29" t="n">
-        <v>964</v>
-      </c>
-      <c r="G29" t="n">
-        <v>954</v>
-      </c>
-      <c r="H29" t="n">
-        <v>972</v>
-      </c>
-      <c r="I29" t="n">
-        <v>981</v>
-      </c>
       <c r="J29" t="n">
-        <v>913</v>
+        <v>1012</v>
       </c>
       <c r="K29" t="n">
-        <v>960</v>
+        <v>983</v>
       </c>
       <c r="L29" t="n">
-        <v>958.2</v>
+        <v>918.4</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>738</v>
+        <v>907</v>
       </c>
       <c r="C30" t="n">
-        <v>968</v>
+        <v>901</v>
       </c>
       <c r="D30" t="n">
-        <v>750</v>
+        <v>929</v>
       </c>
       <c r="E30" t="n">
-        <v>778</v>
+        <v>795</v>
       </c>
       <c r="F30" t="n">
-        <v>900</v>
+        <v>824</v>
       </c>
       <c r="G30" t="n">
-        <v>930</v>
+        <v>963</v>
       </c>
       <c r="H30" t="n">
-        <v>990</v>
+        <v>929</v>
       </c>
       <c r="I30" t="n">
-        <v>971</v>
+        <v>1010</v>
       </c>
       <c r="J30" t="n">
-        <v>760</v>
+        <v>912</v>
       </c>
       <c r="K30" t="n">
-        <v>794</v>
+        <v>976</v>
       </c>
       <c r="L30" t="n">
-        <v>857.9</v>
+        <v>914.6</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>695</v>
+        <v>933</v>
       </c>
       <c r="C31" t="n">
-        <v>1014</v>
+        <v>925</v>
       </c>
       <c r="D31" t="n">
-        <v>875</v>
+        <v>967</v>
       </c>
       <c r="E31" t="n">
-        <v>731</v>
+        <v>1043</v>
       </c>
       <c r="F31" t="n">
-        <v>954</v>
+        <v>869</v>
       </c>
       <c r="G31" t="n">
-        <v>908</v>
+        <v>753</v>
       </c>
       <c r="H31" t="n">
-        <v>945</v>
+        <v>965</v>
       </c>
       <c r="I31" t="n">
-        <v>763</v>
+        <v>833</v>
       </c>
       <c r="J31" t="n">
-        <v>1010</v>
+        <v>964</v>
       </c>
       <c r="K31" t="n">
-        <v>882</v>
+        <v>939</v>
       </c>
       <c r="L31" t="n">
-        <v>877.7</v>
+        <v>919.1</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>843</v>
+        <v>734</v>
       </c>
       <c r="C32" t="n">
-        <v>1010</v>
+        <v>826</v>
       </c>
       <c r="D32" t="n">
-        <v>873</v>
+        <v>779</v>
       </c>
       <c r="E32" t="n">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F32" t="n">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="G32" t="n">
-        <v>838</v>
+        <v>795</v>
       </c>
       <c r="H32" t="n">
-        <v>919</v>
+        <v>870</v>
       </c>
       <c r="I32" t="n">
-        <v>779</v>
+        <v>1043</v>
       </c>
       <c r="J32" t="n">
-        <v>818</v>
+        <v>795</v>
       </c>
       <c r="K32" t="n">
-        <v>836</v>
+        <v>1074</v>
       </c>
       <c r="L32" t="n">
-        <v>872.8</v>
+        <v>871.5</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>1037</v>
+        <v>1000</v>
       </c>
       <c r="C33" t="n">
-        <v>830</v>
+        <v>960</v>
       </c>
       <c r="D33" t="n">
-        <v>754</v>
+        <v>905</v>
       </c>
       <c r="E33" t="n">
-        <v>830</v>
+        <v>872</v>
       </c>
       <c r="F33" t="n">
-        <v>771</v>
+        <v>810</v>
       </c>
       <c r="G33" t="n">
-        <v>837</v>
+        <v>723</v>
       </c>
       <c r="H33" t="n">
-        <v>898</v>
+        <v>833</v>
       </c>
       <c r="I33" t="n">
-        <v>951</v>
+        <v>718</v>
       </c>
       <c r="J33" t="n">
-        <v>1021</v>
+        <v>907</v>
       </c>
       <c r="K33" t="n">
-        <v>801</v>
+        <v>881</v>
       </c>
       <c r="L33" t="n">
-        <v>873</v>
+        <v>860.9</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="C34" t="n">
-        <v>768</v>
+        <v>624</v>
       </c>
       <c r="D34" t="n">
-        <v>885</v>
+        <v>945</v>
       </c>
       <c r="E34" t="n">
-        <v>787</v>
+        <v>928</v>
       </c>
       <c r="F34" t="n">
-        <v>767</v>
+        <v>805</v>
       </c>
       <c r="G34" t="n">
-        <v>749</v>
+        <v>860</v>
       </c>
       <c r="H34" t="n">
-        <v>1019</v>
+        <v>799</v>
       </c>
       <c r="I34" t="n">
-        <v>672</v>
+        <v>829</v>
       </c>
       <c r="J34" t="n">
-        <v>756</v>
+        <v>981</v>
       </c>
       <c r="K34" t="n">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="L34" t="n">
-        <v>812.5</v>
+        <v>847.3</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>877</v>
+        <v>706</v>
       </c>
       <c r="C35" t="n">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="D35" t="n">
-        <v>814</v>
+        <v>860</v>
       </c>
       <c r="E35" t="n">
-        <v>759</v>
+        <v>801</v>
       </c>
       <c r="F35" t="n">
-        <v>888</v>
+        <v>836</v>
       </c>
       <c r="G35" t="n">
-        <v>828</v>
+        <v>728</v>
       </c>
       <c r="H35" t="n">
-        <v>739</v>
+        <v>870</v>
       </c>
       <c r="I35" t="n">
-        <v>723</v>
+        <v>736</v>
       </c>
       <c r="J35" t="n">
-        <v>706</v>
+        <v>788</v>
       </c>
       <c r="K35" t="n">
-        <v>879</v>
+        <v>691</v>
       </c>
       <c r="L35" t="n">
-        <v>806.1</v>
+        <v>785.9</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>773</v>
+        <v>1057</v>
       </c>
       <c r="C36" t="n">
-        <v>1104</v>
+        <v>1010</v>
       </c>
       <c r="D36" t="n">
-        <v>1077</v>
+        <v>931</v>
       </c>
       <c r="E36" t="n">
-        <v>1068</v>
+        <v>914</v>
       </c>
       <c r="F36" t="n">
-        <v>1064</v>
+        <v>1017</v>
       </c>
       <c r="G36" t="n">
-        <v>990</v>
+        <v>1096</v>
       </c>
       <c r="H36" t="n">
-        <v>1068</v>
+        <v>1044</v>
       </c>
       <c r="I36" t="n">
-        <v>1047</v>
+        <v>1040</v>
       </c>
       <c r="J36" t="n">
-        <v>1136</v>
+        <v>1083</v>
       </c>
       <c r="K36" t="n">
-        <v>816</v>
+        <v>845</v>
       </c>
       <c r="L36" t="n">
-        <v>1014.3</v>
+        <v>1003.7</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>967</v>
+        <v>912</v>
       </c>
       <c r="C37" t="n">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D37" t="n">
-        <v>812</v>
+        <v>740</v>
       </c>
       <c r="E37" t="n">
+        <v>809</v>
+      </c>
+      <c r="F37" t="n">
         <v>731</v>
       </c>
-      <c r="F37" t="n">
-        <v>732</v>
-      </c>
       <c r="G37" t="n">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="H37" t="n">
-        <v>949</v>
+        <v>785</v>
       </c>
       <c r="I37" t="n">
-        <v>714</v>
+        <v>762</v>
       </c>
       <c r="J37" t="n">
-        <v>756</v>
+        <v>773</v>
       </c>
       <c r="K37" t="n">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="L37" t="n">
-        <v>811.6</v>
+        <v>796.1</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>859</v>
+        <v>988</v>
       </c>
       <c r="C38" t="n">
         <v>799</v>
       </c>
       <c r="D38" t="n">
-        <v>900</v>
+        <v>744</v>
       </c>
       <c r="E38" t="n">
-        <v>864</v>
+        <v>833</v>
       </c>
       <c r="F38" t="n">
-        <v>774</v>
+        <v>809</v>
       </c>
       <c r="G38" t="n">
-        <v>761</v>
+        <v>843</v>
       </c>
       <c r="H38" t="n">
-        <v>919</v>
+        <v>800</v>
       </c>
       <c r="I38" t="n">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="J38" t="n">
-        <v>1019</v>
+        <v>794</v>
       </c>
       <c r="K38" t="n">
-        <v>946</v>
+        <v>1049</v>
       </c>
       <c r="L38" t="n">
-        <v>871.2</v>
+        <v>860.6</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>827</v>
+        <v>854</v>
       </c>
       <c r="C39" t="n">
-        <v>772</v>
+        <v>860</v>
       </c>
       <c r="D39" t="n">
-        <v>823</v>
+        <v>799</v>
       </c>
       <c r="E39" t="n">
-        <v>948</v>
+        <v>865</v>
       </c>
       <c r="F39" t="n">
-        <v>831</v>
+        <v>759</v>
       </c>
       <c r="G39" t="n">
-        <v>801</v>
+        <v>811</v>
       </c>
       <c r="H39" t="n">
-        <v>813</v>
+        <v>759</v>
       </c>
       <c r="I39" t="n">
-        <v>953</v>
+        <v>1089</v>
       </c>
       <c r="J39" t="n">
-        <v>768</v>
+        <v>847</v>
       </c>
       <c r="K39" t="n">
-        <v>894</v>
+        <v>846</v>
       </c>
       <c r="L39" t="n">
-        <v>843</v>
+        <v>848.9</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>785</v>
+        <v>837</v>
       </c>
       <c r="C40" t="n">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="D40" t="n">
-        <v>783</v>
+        <v>1027</v>
       </c>
       <c r="E40" t="n">
-        <v>769</v>
+        <v>848</v>
       </c>
       <c r="F40" t="n">
-        <v>923</v>
+        <v>958</v>
       </c>
       <c r="G40" t="n">
-        <v>997</v>
+        <v>920</v>
       </c>
       <c r="H40" t="n">
-        <v>875</v>
+        <v>943</v>
       </c>
       <c r="I40" t="n">
-        <v>988</v>
+        <v>841</v>
       </c>
       <c r="J40" t="n">
-        <v>936</v>
+        <v>1040</v>
       </c>
       <c r="K40" t="n">
-        <v>924</v>
+        <v>943</v>
       </c>
       <c r="L40" t="n">
-        <v>891.5</v>
+        <v>928.7</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>1117</v>
+        <v>882</v>
       </c>
       <c r="C41" t="n">
-        <v>895</v>
+        <v>735</v>
       </c>
       <c r="D41" t="n">
-        <v>862</v>
+        <v>964</v>
       </c>
       <c r="E41" t="n">
-        <v>868</v>
+        <v>800</v>
       </c>
       <c r="F41" t="n">
-        <v>740</v>
+        <v>957</v>
       </c>
       <c r="G41" t="n">
-        <v>922</v>
+        <v>714</v>
       </c>
       <c r="H41" t="n">
-        <v>896</v>
+        <v>914</v>
       </c>
       <c r="I41" t="n">
-        <v>1099</v>
+        <v>753</v>
       </c>
       <c r="J41" t="n">
-        <v>984</v>
+        <v>956</v>
       </c>
       <c r="K41" t="n">
-        <v>908</v>
+        <v>858</v>
       </c>
       <c r="L41" t="n">
-        <v>929.1</v>
+        <v>853.3</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="C42" t="n">
-        <v>927</v>
+        <v>677</v>
       </c>
       <c r="D42" t="n">
-        <v>730</v>
+        <v>685</v>
       </c>
       <c r="E42" t="n">
-        <v>921</v>
+        <v>773</v>
       </c>
       <c r="F42" t="n">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="G42" t="n">
-        <v>862</v>
+        <v>977</v>
       </c>
       <c r="H42" t="n">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I42" t="n">
-        <v>692</v>
+        <v>732</v>
       </c>
       <c r="J42" t="n">
-        <v>878</v>
+        <v>718</v>
       </c>
       <c r="K42" t="n">
-        <v>678</v>
+        <v>842</v>
       </c>
       <c r="L42" t="n">
-        <v>805.8</v>
+        <v>778.4</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>760</v>
+        <v>852</v>
       </c>
       <c r="C43" t="n">
-        <v>934</v>
+        <v>885</v>
       </c>
       <c r="D43" t="n">
-        <v>719</v>
+        <v>989</v>
       </c>
       <c r="E43" t="n">
-        <v>884</v>
+        <v>951</v>
       </c>
       <c r="F43" t="n">
-        <v>943</v>
+        <v>931</v>
       </c>
       <c r="G43" t="n">
-        <v>1065</v>
+        <v>910</v>
       </c>
       <c r="H43" t="n">
-        <v>972</v>
+        <v>796</v>
       </c>
       <c r="I43" t="n">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="J43" t="n">
-        <v>955</v>
+        <v>948</v>
       </c>
       <c r="K43" t="n">
-        <v>802</v>
+        <v>755</v>
       </c>
       <c r="L43" t="n">
-        <v>892</v>
+        <v>892.3</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>797</v>
+        <v>830</v>
       </c>
       <c r="C44" t="n">
-        <v>862</v>
+        <v>893</v>
       </c>
       <c r="D44" t="n">
-        <v>829</v>
+        <v>755</v>
       </c>
       <c r="E44" t="n">
-        <v>877</v>
+        <v>844</v>
       </c>
       <c r="F44" t="n">
-        <v>798</v>
+        <v>747</v>
       </c>
       <c r="G44" t="n">
-        <v>898</v>
+        <v>807</v>
       </c>
       <c r="H44" t="n">
-        <v>921</v>
+        <v>828</v>
       </c>
       <c r="I44" t="n">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="J44" t="n">
-        <v>866</v>
+        <v>739</v>
       </c>
       <c r="K44" t="n">
-        <v>950</v>
+        <v>991</v>
       </c>
       <c r="L44" t="n">
-        <v>860</v>
+        <v>822.6</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>980</v>
+        <v>999</v>
       </c>
       <c r="C45" t="n">
-        <v>1020</v>
+        <v>926</v>
       </c>
       <c r="D45" t="n">
-        <v>1043</v>
+        <v>820</v>
       </c>
       <c r="E45" t="n">
-        <v>964</v>
+        <v>858</v>
       </c>
       <c r="F45" t="n">
-        <v>1030</v>
+        <v>928</v>
       </c>
       <c r="G45" t="n">
-        <v>1110</v>
+        <v>1002</v>
       </c>
       <c r="H45" t="n">
-        <v>1037</v>
+        <v>936</v>
       </c>
       <c r="I45" t="n">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="J45" t="n">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="K45" t="n">
-        <v>850</v>
+        <v>939</v>
       </c>
       <c r="L45" t="n">
-        <v>977</v>
+        <v>914.8</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>755</v>
+        <v>865</v>
       </c>
       <c r="C46" t="n">
-        <v>878</v>
+        <v>965</v>
       </c>
       <c r="D46" t="n">
-        <v>794</v>
+        <v>890</v>
       </c>
       <c r="E46" t="n">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="F46" t="n">
-        <v>876</v>
+        <v>903</v>
       </c>
       <c r="G46" t="n">
-        <v>946</v>
+        <v>800</v>
       </c>
       <c r="H46" t="n">
-        <v>722</v>
+        <v>824</v>
       </c>
       <c r="I46" t="n">
-        <v>900</v>
+        <v>940</v>
       </c>
       <c r="J46" t="n">
-        <v>856</v>
+        <v>834</v>
       </c>
       <c r="K46" t="n">
-        <v>953</v>
+        <v>968</v>
       </c>
       <c r="L46" t="n">
-        <v>852.6</v>
+        <v>883.3</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>907</v>
+        <v>827</v>
       </c>
       <c r="C47" t="n">
-        <v>994</v>
+        <v>858</v>
       </c>
       <c r="D47" t="n">
-        <v>909</v>
+        <v>1015</v>
       </c>
       <c r="E47" t="n">
-        <v>909</v>
+        <v>884</v>
       </c>
       <c r="F47" t="n">
-        <v>976</v>
+        <v>903</v>
       </c>
       <c r="G47" t="n">
-        <v>1036</v>
+        <v>765</v>
       </c>
       <c r="H47" t="n">
-        <v>947</v>
+        <v>1056</v>
       </c>
       <c r="I47" t="n">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="J47" t="n">
-        <v>978</v>
+        <v>1035</v>
       </c>
       <c r="K47" t="n">
-        <v>887</v>
+        <v>1038</v>
       </c>
       <c r="L47" t="n">
-        <v>950.8</v>
+        <v>934.5</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>811</v>
+        <v>852</v>
       </c>
       <c r="C48" t="n">
-        <v>861</v>
+        <v>925</v>
       </c>
       <c r="D48" t="n">
-        <v>912</v>
+        <v>1077</v>
       </c>
       <c r="E48" t="n">
-        <v>1070</v>
+        <v>891</v>
       </c>
       <c r="F48" t="n">
-        <v>1022</v>
+        <v>928</v>
       </c>
       <c r="G48" t="n">
-        <v>906</v>
+        <v>943</v>
       </c>
       <c r="H48" t="n">
-        <v>905</v>
+        <v>853</v>
       </c>
       <c r="I48" t="n">
-        <v>842</v>
+        <v>823</v>
       </c>
       <c r="J48" t="n">
-        <v>828</v>
+        <v>846</v>
       </c>
       <c r="K48" t="n">
-        <v>832</v>
+        <v>904</v>
       </c>
       <c r="L48" t="n">
-        <v>898.9</v>
+        <v>904.2</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>852</v>
+        <v>924</v>
       </c>
       <c r="C49" t="n">
-        <v>924</v>
+        <v>801</v>
       </c>
       <c r="D49" t="n">
-        <v>843</v>
+        <v>739</v>
       </c>
       <c r="E49" t="n">
-        <v>832</v>
+        <v>883</v>
       </c>
       <c r="F49" t="n">
-        <v>772</v>
+        <v>905</v>
       </c>
       <c r="G49" t="n">
-        <v>944</v>
+        <v>921</v>
       </c>
       <c r="H49" t="n">
-        <v>791</v>
+        <v>862</v>
       </c>
       <c r="I49" t="n">
-        <v>1077</v>
+        <v>886</v>
       </c>
       <c r="J49" t="n">
-        <v>838</v>
+        <v>909</v>
       </c>
       <c r="K49" t="n">
-        <v>874</v>
+        <v>989</v>
       </c>
       <c r="L49" t="n">
-        <v>874.7</v>
+        <v>881.9</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>998</v>
+        <v>934</v>
       </c>
       <c r="C50" t="n">
-        <v>1038</v>
+        <v>953</v>
       </c>
       <c r="D50" t="n">
-        <v>944</v>
+        <v>987</v>
       </c>
       <c r="E50" t="n">
-        <v>921</v>
+        <v>782</v>
       </c>
       <c r="F50" t="n">
-        <v>941</v>
+        <v>974</v>
       </c>
       <c r="G50" t="n">
-        <v>1057</v>
+        <v>865</v>
       </c>
       <c r="H50" t="n">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="I50" t="n">
-        <v>921</v>
+        <v>907</v>
       </c>
       <c r="J50" t="n">
-        <v>892</v>
+        <v>907</v>
       </c>
       <c r="K50" t="n">
-        <v>898</v>
+        <v>938</v>
       </c>
       <c r="L50" t="n">
-        <v>956</v>
+        <v>920.3</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>860</v>
+        <v>916</v>
       </c>
       <c r="C51" t="n">
-        <v>799</v>
+        <v>951</v>
       </c>
       <c r="D51" t="n">
-        <v>910</v>
+        <v>803</v>
       </c>
       <c r="E51" t="n">
-        <v>889</v>
+        <v>1000</v>
       </c>
       <c r="F51" t="n">
-        <v>873</v>
+        <v>826</v>
       </c>
       <c r="G51" t="n">
-        <v>1026</v>
+        <v>936</v>
       </c>
       <c r="H51" t="n">
-        <v>747</v>
+        <v>917</v>
       </c>
       <c r="I51" t="n">
-        <v>903</v>
+        <v>866</v>
       </c>
       <c r="J51" t="n">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="K51" t="n">
-        <v>862</v>
+        <v>977</v>
       </c>
       <c r="L51" t="n">
-        <v>873.8</v>
+        <v>907.1</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>867</v>
+        <v>887.5</v>
       </c>
       <c r="C52" t="n">
-        <v>887.26</v>
+        <v>860.6799999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>878.74</v>
+        <v>884</v>
       </c>
       <c r="E52" t="n">
-        <v>883.96</v>
+        <v>882</v>
       </c>
       <c r="F52" t="n">
-        <v>872.6799999999999</v>
+        <v>880.24</v>
       </c>
       <c r="G52" t="n">
-        <v>918.48</v>
+        <v>887</v>
       </c>
       <c r="H52" t="n">
-        <v>886.38</v>
+        <v>878.48</v>
       </c>
       <c r="I52" t="n">
-        <v>890.34</v>
+        <v>895.12</v>
       </c>
       <c r="J52" t="n">
-        <v>884.98</v>
+        <v>887</v>
       </c>
       <c r="K52" t="n">
-        <v>898.48</v>
+        <v>907.0599999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>886.83</v>
+        <v>884.908</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>9.211516380310059</v>
+        <v>7.382179260253906</v>
       </c>
       <c r="C2" t="n">
-        <v>8.851783514022827</v>
+        <v>7.35089635848999</v>
       </c>
       <c r="D2" t="n">
-        <v>7.130318880081177</v>
+        <v>8.680920362472534</v>
       </c>
       <c r="E2" t="n">
-        <v>8.462948560714722</v>
+        <v>8.701857805252075</v>
       </c>
       <c r="F2" t="n">
-        <v>6.797164678573608</v>
+        <v>8.644478559494019</v>
       </c>
       <c r="G2" t="n">
-        <v>8.342721939086914</v>
+        <v>7.62408709526062</v>
       </c>
       <c r="H2" t="n">
-        <v>7.136309146881104</v>
+        <v>9.100872039794922</v>
       </c>
       <c r="I2" t="n">
-        <v>7.486910343170166</v>
+        <v>8.233561277389526</v>
       </c>
       <c r="J2" t="n">
-        <v>7.790115833282471</v>
+        <v>8.682895183563232</v>
       </c>
       <c r="K2" t="n">
-        <v>9.465360164642334</v>
+        <v>8.35076379776001</v>
       </c>
       <c r="L2" t="n">
-        <v>8.067514944076539</v>
+        <v>8.275251173973084</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>7.638542413711548</v>
+        <v>7.495028018951416</v>
       </c>
       <c r="C3" t="n">
-        <v>7.090439319610596</v>
+        <v>7.798704624176025</v>
       </c>
       <c r="D3" t="n">
-        <v>8.027511119842529</v>
+        <v>7.173823595046997</v>
       </c>
       <c r="E3" t="n">
-        <v>7.623552560806274</v>
+        <v>8.051533699035645</v>
       </c>
       <c r="F3" t="n">
-        <v>8.359608173370361</v>
+        <v>6.969375848770142</v>
       </c>
       <c r="G3" t="n">
-        <v>7.751345634460449</v>
+        <v>9.15118145942688</v>
       </c>
       <c r="H3" t="n">
-        <v>7.447037935256958</v>
+        <v>7.762322187423706</v>
       </c>
       <c r="I3" t="n">
-        <v>7.960182666778564</v>
+        <v>7.311458826065063</v>
       </c>
       <c r="J3" t="n">
-        <v>9.33820366859436</v>
+        <v>8.997600555419922</v>
       </c>
       <c r="K3" t="n">
-        <v>7.044111013412476</v>
+        <v>7.708446741104126</v>
       </c>
       <c r="L3" t="n">
-        <v>7.828053450584411</v>
+        <v>7.841947555541992</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>6.483950853347778</v>
+        <v>8.543276309967041</v>
       </c>
       <c r="C4" t="n">
-        <v>6.741316556930542</v>
+        <v>7.138906002044678</v>
       </c>
       <c r="D4" t="n">
-        <v>6.666016101837158</v>
+        <v>7.419661283493042</v>
       </c>
       <c r="E4" t="n">
-        <v>7.968696117401123</v>
+        <v>8.400137662887573</v>
       </c>
       <c r="F4" t="n">
-        <v>6.095953702926636</v>
+        <v>24.21381163597107</v>
       </c>
       <c r="G4" t="n">
-        <v>6.755262613296509</v>
+        <v>9.299344301223755</v>
       </c>
       <c r="H4" t="n">
-        <v>8.756692171096802</v>
+        <v>6.871642112731934</v>
       </c>
       <c r="I4" t="n">
-        <v>6.398197412490845</v>
+        <v>7.634102821350098</v>
       </c>
       <c r="J4" t="n">
-        <v>7.385154962539673</v>
+        <v>6.411298513412476</v>
       </c>
       <c r="K4" t="n">
-        <v>8.851442813873291</v>
+        <v>6.593368768692017</v>
       </c>
       <c r="L4" t="n">
-        <v>7.210268330574036</v>
+        <v>9.252554941177369</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>9.395515918731689</v>
+        <v>8.044100999832153</v>
       </c>
       <c r="C5" t="n">
-        <v>6.571267127990723</v>
+        <v>6.777340888977051</v>
       </c>
       <c r="D5" t="n">
-        <v>6.536826372146606</v>
+        <v>8.310854196548462</v>
       </c>
       <c r="E5" t="n">
-        <v>8.501851797103882</v>
+        <v>6.135626316070557</v>
       </c>
       <c r="F5" t="n">
-        <v>8.133772611618042</v>
+        <v>9.725238561630249</v>
       </c>
       <c r="G5" t="n">
-        <v>8.226034879684448</v>
+        <v>6.579875469207764</v>
       </c>
       <c r="H5" t="n">
-        <v>8.942689657211304</v>
+        <v>6.526501178741455</v>
       </c>
       <c r="I5" t="n">
-        <v>6.199184417724609</v>
+        <v>9.007572650909424</v>
       </c>
       <c r="J5" t="n">
-        <v>6.337345123291016</v>
+        <v>7.190780162811279</v>
       </c>
       <c r="K5" t="n">
-        <v>8.586143970489502</v>
+        <v>9.54118537902832</v>
       </c>
       <c r="L5" t="n">
-        <v>7.743063187599182</v>
+        <v>7.783907580375671</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>6.078034400939941</v>
+        <v>7.005866050720215</v>
       </c>
       <c r="C6" t="n">
-        <v>7.947241544723511</v>
+        <v>5.70265793800354</v>
       </c>
       <c r="D6" t="n">
-        <v>5.994707107543945</v>
+        <v>6.039283514022827</v>
       </c>
       <c r="E6" t="n">
-        <v>6.519905567169189</v>
+        <v>6.783350229263306</v>
       </c>
       <c r="F6" t="n">
-        <v>7.106988191604614</v>
+        <v>7.185796737670898</v>
       </c>
       <c r="G6" t="n">
-        <v>6.141005277633667</v>
+        <v>6.377496719360352</v>
       </c>
       <c r="H6" t="n">
-        <v>6.793792963027954</v>
+        <v>6.153509378433228</v>
       </c>
       <c r="I6" t="n">
-        <v>6.35444712638855</v>
+        <v>9.0035560131073</v>
       </c>
       <c r="J6" t="n">
-        <v>6.334020853042603</v>
+        <v>5.762996673583984</v>
       </c>
       <c r="K6" t="n">
-        <v>5.643295526504517</v>
+        <v>8.718832492828369</v>
       </c>
       <c r="L6" t="n">
-        <v>6.491343855857849</v>
+        <v>6.873334574699402</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>7.277052640914917</v>
+        <v>9.488295078277588</v>
       </c>
       <c r="C7" t="n">
-        <v>7.893432140350342</v>
+        <v>7.531420230865479</v>
       </c>
       <c r="D7" t="n">
-        <v>7.346757411956787</v>
+        <v>7.30102276802063</v>
       </c>
       <c r="E7" t="n">
-        <v>8.925779104232788</v>
+        <v>7.706444025039673</v>
       </c>
       <c r="F7" t="n">
-        <v>8.534741401672363</v>
+        <v>8.505379915237427</v>
       </c>
       <c r="G7" t="n">
-        <v>8.58016037940979</v>
+        <v>9.565084457397461</v>
       </c>
       <c r="H7" t="n">
-        <v>7.891361951828003</v>
+        <v>8.592375040054321</v>
       </c>
       <c r="I7" t="n">
-        <v>8.13973069190979</v>
+        <v>9.076507329940796</v>
       </c>
       <c r="J7" t="n">
-        <v>9.384623765945435</v>
+        <v>7.082459211349487</v>
       </c>
       <c r="K7" t="n">
-        <v>8.280384063720703</v>
+        <v>10.23890709877014</v>
       </c>
       <c r="L7" t="n">
-        <v>8.225402355194092</v>
+        <v>8.5087895154953</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>9.827948093414307</v>
+        <v>7.669000387191772</v>
       </c>
       <c r="C8" t="n">
-        <v>8.024529695510864</v>
+        <v>7.497888803482056</v>
       </c>
       <c r="D8" t="n">
-        <v>7.700872182846069</v>
+        <v>8.908732175827026</v>
       </c>
       <c r="E8" t="n">
-        <v>8.207063436508179</v>
+        <v>8.741238355636597</v>
       </c>
       <c r="F8" t="n">
-        <v>7.913379669189453</v>
+        <v>8.28538966178894</v>
       </c>
       <c r="G8" t="n">
-        <v>6.988183498382568</v>
+        <v>8.346224546432495</v>
       </c>
       <c r="H8" t="n">
-        <v>9.839926719665527</v>
+        <v>7.40911865234375</v>
       </c>
       <c r="I8" t="n">
-        <v>7.107235670089722</v>
+        <v>8.658439159393311</v>
       </c>
       <c r="J8" t="n">
-        <v>8.737735509872437</v>
+        <v>7.444072961807251</v>
       </c>
       <c r="K8" t="n">
-        <v>8.667451143264771</v>
+        <v>9.165133714675903</v>
       </c>
       <c r="L8" t="n">
-        <v>8.301432561874389</v>
+        <v>8.212523841857911</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>8.90658974647522</v>
+        <v>8.942694664001465</v>
       </c>
       <c r="C9" t="n">
-        <v>8.82202672958374</v>
+        <v>9.760661363601685</v>
       </c>
       <c r="D9" t="n">
-        <v>8.460519790649414</v>
+        <v>7.809099912643433</v>
       </c>
       <c r="E9" t="n">
-        <v>7.290505647659302</v>
+        <v>7.285912990570068</v>
       </c>
       <c r="F9" t="n">
-        <v>8.391660928726196</v>
+        <v>7.389183521270752</v>
       </c>
       <c r="G9" t="n">
-        <v>7.059121608734131</v>
+        <v>7.710341930389404</v>
       </c>
       <c r="H9" t="n">
-        <v>6.988300085067749</v>
+        <v>7.112862586975098</v>
       </c>
       <c r="I9" t="n">
-        <v>7.59622859954834</v>
+        <v>7.636038541793823</v>
       </c>
       <c r="J9" t="n">
-        <v>7.651593685150146</v>
+        <v>8.826494455337524</v>
       </c>
       <c r="K9" t="n">
-        <v>9.154654502868652</v>
+        <v>8.790113925933838</v>
       </c>
       <c r="L9" t="n">
-        <v>8.032120132446289</v>
+        <v>8.126340389251709</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>6.323083877563477</v>
+        <v>7.638535261154175</v>
       </c>
       <c r="C10" t="n">
-        <v>6.652671098709106</v>
+        <v>8.477386474609375</v>
       </c>
       <c r="D10" t="n">
-        <v>8.255023717880249</v>
+        <v>7.439568758010864</v>
       </c>
       <c r="E10" t="n">
-        <v>8.31882381439209</v>
+        <v>6.999662160873413</v>
       </c>
       <c r="F10" t="n">
-        <v>6.700055837631226</v>
+        <v>6.17628288269043</v>
       </c>
       <c r="G10" t="n">
-        <v>7.658328294754028</v>
+        <v>6.6390700340271</v>
       </c>
       <c r="H10" t="n">
-        <v>6.356967687606812</v>
+        <v>8.24449610710144</v>
       </c>
       <c r="I10" t="n">
-        <v>6.639208316802979</v>
+        <v>9.905736684799194</v>
       </c>
       <c r="J10" t="n">
-        <v>6.162450790405273</v>
+        <v>7.426071166992188</v>
       </c>
       <c r="K10" t="n">
-        <v>8.274954319000244</v>
+        <v>8.558208227157593</v>
       </c>
       <c r="L10" t="n">
-        <v>7.134156775474549</v>
+        <v>7.750501775741578</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>7.104987621307373</v>
+        <v>6.774246454238892</v>
       </c>
       <c r="C11" t="n">
-        <v>8.128331661224365</v>
+        <v>7.074492692947388</v>
       </c>
       <c r="D11" t="n">
-        <v>11.0392758846283</v>
+        <v>7.770738124847412</v>
       </c>
       <c r="E11" t="n">
-        <v>7.745333671569824</v>
+        <v>6.764767169952393</v>
       </c>
       <c r="F11" t="n">
-        <v>8.313858032226562</v>
+        <v>6.795719861984253</v>
       </c>
       <c r="G11" t="n">
-        <v>7.300496816635132</v>
+        <v>7.54126501083374</v>
       </c>
       <c r="H11" t="n">
-        <v>7.509950876235962</v>
+        <v>6.782725811004639</v>
       </c>
       <c r="I11" t="n">
-        <v>8.517314910888672</v>
+        <v>8.551685571670532</v>
       </c>
       <c r="J11" t="n">
-        <v>8.823049306869507</v>
+        <v>9.064906358718872</v>
       </c>
       <c r="K11" t="n">
-        <v>9.056451320648193</v>
+        <v>7.207630157470703</v>
       </c>
       <c r="L11" t="n">
-        <v>8.353905010223389</v>
+        <v>7.432817721366883</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>8.980112552642822</v>
+        <v>9.07145881652832</v>
       </c>
       <c r="C12" t="n">
-        <v>10.87818050384521</v>
+        <v>8.713304758071899</v>
       </c>
       <c r="D12" t="n">
-        <v>8.000710964202881</v>
+        <v>9.283798933029175</v>
       </c>
       <c r="E12" t="n">
-        <v>10.24085450172424</v>
+        <v>10.34205746650696</v>
       </c>
       <c r="F12" t="n">
-        <v>7.419675588607788</v>
+        <v>7.433117866516113</v>
       </c>
       <c r="G12" t="n">
-        <v>10.34556126594543</v>
+        <v>8.38114070892334</v>
       </c>
       <c r="H12" t="n">
-        <v>11.49155187606812</v>
+        <v>9.431500196456909</v>
       </c>
       <c r="I12" t="n">
-        <v>9.418960094451904</v>
+        <v>7.814141988754272</v>
       </c>
       <c r="J12" t="n">
-        <v>9.327723741531372</v>
+        <v>9.420999526977539</v>
       </c>
       <c r="K12" t="n">
-        <v>10.01842761039734</v>
+        <v>7.377692461013794</v>
       </c>
       <c r="L12" t="n">
-        <v>9.612175869941712</v>
+        <v>8.726921272277831</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>6.984305620193481</v>
+        <v>7.389239549636841</v>
       </c>
       <c r="C13" t="n">
-        <v>7.440102577209473</v>
+        <v>7.160369634628296</v>
       </c>
       <c r="D13" t="n">
-        <v>8.575167179107666</v>
+        <v>6.113588809967041</v>
       </c>
       <c r="E13" t="n">
-        <v>7.491019725799561</v>
+        <v>7.895493030548096</v>
       </c>
       <c r="F13" t="n">
-        <v>7.308462142944336</v>
+        <v>6.474646091461182</v>
       </c>
       <c r="G13" t="n">
-        <v>7.402743339538574</v>
+        <v>7.726384878158569</v>
       </c>
       <c r="H13" t="n">
-        <v>6.207327842712402</v>
+        <v>6.721015930175781</v>
       </c>
       <c r="I13" t="n">
-        <v>7.550367832183838</v>
+        <v>7.803709745407104</v>
       </c>
       <c r="J13" t="n">
-        <v>6.926479339599609</v>
+        <v>6.647714376449585</v>
       </c>
       <c r="K13" t="n">
-        <v>7.398750305175781</v>
+        <v>7.742873430252075</v>
       </c>
       <c r="L13" t="n">
-        <v>7.328472590446472</v>
+        <v>7.167503547668457</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>7.967756986618042</v>
+        <v>7.849111318588257</v>
       </c>
       <c r="C14" t="n">
-        <v>7.9098961353302</v>
+        <v>7.422117948532104</v>
       </c>
       <c r="D14" t="n">
-        <v>9.853827953338623</v>
+        <v>7.14825963973999</v>
       </c>
       <c r="E14" t="n">
-        <v>7.359334945678711</v>
+        <v>7.096401691436768</v>
       </c>
       <c r="F14" t="n">
-        <v>7.928406476974487</v>
+        <v>8.443467855453491</v>
       </c>
       <c r="G14" t="n">
-        <v>9.568681955337524</v>
+        <v>7.094413280487061</v>
       </c>
       <c r="H14" t="n">
-        <v>9.646867036819458</v>
+        <v>7.298894166946411</v>
       </c>
       <c r="I14" t="n">
-        <v>8.871894359588623</v>
+        <v>7.757755756378174</v>
       </c>
       <c r="J14" t="n">
-        <v>8.98359489440918</v>
+        <v>7.629053592681885</v>
       </c>
       <c r="K14" t="n">
-        <v>7.73901104927063</v>
+        <v>9.643407583236694</v>
       </c>
       <c r="L14" t="n">
-        <v>8.582927179336547</v>
+        <v>7.738288283348083</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>9.266572952270508</v>
+        <v>6.648045063018799</v>
       </c>
       <c r="C15" t="n">
-        <v>7.562828302383423</v>
+        <v>6.601166486740112</v>
       </c>
       <c r="D15" t="n">
-        <v>7.660560846328735</v>
+        <v>10.37158298492432</v>
       </c>
       <c r="E15" t="n">
-        <v>8.284894227981567</v>
+        <v>6.846546173095703</v>
       </c>
       <c r="F15" t="n">
-        <v>7.150830030441284</v>
+        <v>7.401126384735107</v>
       </c>
       <c r="G15" t="n">
-        <v>7.954223155975342</v>
+        <v>9.009086847305298</v>
       </c>
       <c r="H15" t="n">
-        <v>8.264896869659424</v>
+        <v>9.678347110748291</v>
       </c>
       <c r="I15" t="n">
-        <v>6.868015289306641</v>
+        <v>7.584668397903442</v>
       </c>
       <c r="J15" t="n">
-        <v>7.023105621337891</v>
+        <v>8.058447360992432</v>
       </c>
       <c r="K15" t="n">
-        <v>8.026566028594971</v>
+        <v>7.105400800704956</v>
       </c>
       <c r="L15" t="n">
-        <v>7.806249332427979</v>
+        <v>7.930441761016846</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>8.833476543426514</v>
+        <v>7.540769338607788</v>
       </c>
       <c r="C16" t="n">
-        <v>7.62603235244751</v>
+        <v>7.250561237335205</v>
       </c>
       <c r="D16" t="n">
-        <v>6.790165424346924</v>
+        <v>6.906893491744995</v>
       </c>
       <c r="E16" t="n">
-        <v>7.214606761932373</v>
+        <v>8.373154163360596</v>
       </c>
       <c r="F16" t="n">
-        <v>6.880971670150757</v>
+        <v>7.314857959747314</v>
       </c>
       <c r="G16" t="n">
-        <v>8.769141912460327</v>
+        <v>8.397589921951294</v>
       </c>
       <c r="H16" t="n">
-        <v>7.361258506774902</v>
+        <v>7.162729501724243</v>
       </c>
       <c r="I16" t="n">
-        <v>8.035524129867554</v>
+        <v>7.720826864242554</v>
       </c>
       <c r="J16" t="n">
-        <v>6.899924993515015</v>
+        <v>7.19813871383667</v>
       </c>
       <c r="K16" t="n">
-        <v>7.662451505661011</v>
+        <v>8.353716850280762</v>
       </c>
       <c r="L16" t="n">
-        <v>7.607355380058289</v>
+        <v>7.621923804283142</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>6.992572069168091</v>
+        <v>8.12778639793396</v>
       </c>
       <c r="C17" t="n">
-        <v>8.020103216171265</v>
+        <v>10.78152894973755</v>
       </c>
       <c r="D17" t="n">
-        <v>8.921247720718384</v>
+        <v>7.769741296768188</v>
       </c>
       <c r="E17" t="n">
-        <v>8.502382278442383</v>
+        <v>9.87736701965332</v>
       </c>
       <c r="F17" t="n">
-        <v>8.475433349609375</v>
+        <v>7.57718825340271</v>
       </c>
       <c r="G17" t="n">
-        <v>7.844575881958008</v>
+        <v>9.017023324966431</v>
       </c>
       <c r="H17" t="n">
-        <v>7.260116815567017</v>
+        <v>9.734662532806396</v>
       </c>
       <c r="I17" t="n">
-        <v>7.928264856338501</v>
+        <v>7.129369020462036</v>
       </c>
       <c r="J17" t="n">
-        <v>7.607642650604248</v>
+        <v>7.156809091567993</v>
       </c>
       <c r="K17" t="n">
-        <v>10.52364015579224</v>
+        <v>7.415977478027344</v>
       </c>
       <c r="L17" t="n">
-        <v>8.207597899436951</v>
+        <v>8.458745336532592</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>6.668832778930664</v>
+        <v>6.939449310302734</v>
       </c>
       <c r="C18" t="n">
-        <v>7.001761913299561</v>
+        <v>6.682108640670776</v>
       </c>
       <c r="D18" t="n">
-        <v>6.972358465194702</v>
+        <v>9.510755300521851</v>
       </c>
       <c r="E18" t="n">
-        <v>8.157759428024292</v>
+        <v>6.938503265380859</v>
       </c>
       <c r="F18" t="n">
-        <v>6.60781455039978</v>
+        <v>6.541502714157104</v>
       </c>
       <c r="G18" t="n">
-        <v>6.793808221817017</v>
+        <v>9.842378377914429</v>
       </c>
       <c r="H18" t="n">
-        <v>6.73747444152832</v>
+        <v>6.865617275238037</v>
       </c>
       <c r="I18" t="n">
-        <v>8.511342525482178</v>
+        <v>9.464361906051636</v>
       </c>
       <c r="J18" t="n">
-        <v>9.801090240478516</v>
+        <v>6.638208389282227</v>
       </c>
       <c r="K18" t="n">
-        <v>7.155372381210327</v>
+        <v>6.782859086990356</v>
       </c>
       <c r="L18" t="n">
-        <v>7.440761494636535</v>
+        <v>7.620574426651001</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>7.553852558135986</v>
+        <v>7.209742546081543</v>
       </c>
       <c r="C19" t="n">
-        <v>9.516739368438721</v>
+        <v>6.537014007568359</v>
       </c>
       <c r="D19" t="n">
-        <v>6.649206399917603</v>
+        <v>6.936432361602783</v>
       </c>
       <c r="E19" t="n">
-        <v>6.743941307067871</v>
+        <v>9.142722606658936</v>
       </c>
       <c r="F19" t="n">
-        <v>6.553439855575562</v>
+        <v>7.495990753173828</v>
       </c>
       <c r="G19" t="n">
-        <v>8.087443828582764</v>
+        <v>9.263503074645996</v>
       </c>
       <c r="H19" t="n">
-        <v>6.490599155426025</v>
+        <v>7.92230224609375</v>
       </c>
       <c r="I19" t="n">
-        <v>7.951773881912231</v>
+        <v>8.506806612014771</v>
       </c>
       <c r="J19" t="n">
-        <v>7.179312944412231</v>
+        <v>7.168737888336182</v>
       </c>
       <c r="K19" t="n">
-        <v>9.084599256515503</v>
+        <v>9.031353235244751</v>
       </c>
       <c r="L19" t="n">
-        <v>7.58109085559845</v>
+        <v>7.92146053314209</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>6.961747884750366</v>
+        <v>10.39095377922058</v>
       </c>
       <c r="C20" t="n">
-        <v>7.568707942962646</v>
+        <v>8.244554281234741</v>
       </c>
       <c r="D20" t="n">
-        <v>8.373171806335449</v>
+        <v>10.36701416969299</v>
       </c>
       <c r="E20" t="n">
-        <v>8.182163238525391</v>
+        <v>7.371314287185669</v>
       </c>
       <c r="F20" t="n">
-        <v>7.756727457046509</v>
+        <v>8.368219614028931</v>
       </c>
       <c r="G20" t="n">
-        <v>7.166756868362427</v>
+        <v>8.808081150054932</v>
       </c>
       <c r="H20" t="n">
-        <v>7.773688077926636</v>
+        <v>9.74113392829895</v>
       </c>
       <c r="I20" t="n">
-        <v>7.078462600708008</v>
+        <v>7.635131120681763</v>
       </c>
       <c r="J20" t="n">
-        <v>7.136306047439575</v>
+        <v>7.471548318862915</v>
       </c>
       <c r="K20" t="n">
-        <v>11.196448802948</v>
+        <v>6.828255891799927</v>
       </c>
       <c r="L20" t="n">
-        <v>7.9194180727005</v>
+        <v>8.52262065410614</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>8.152708292007446</v>
+        <v>8.107405424118042</v>
       </c>
       <c r="C21" t="n">
-        <v>8.66039514541626</v>
+        <v>6.870098352432251</v>
       </c>
       <c r="D21" t="n">
-        <v>8.938697099685669</v>
+        <v>8.359269380569458</v>
       </c>
       <c r="E21" t="n">
-        <v>7.525350093841553</v>
+        <v>7.35435962677002</v>
       </c>
       <c r="F21" t="n">
-        <v>7.868926763534546</v>
+        <v>9.714198589324951</v>
       </c>
       <c r="G21" t="n">
-        <v>7.121312856674194</v>
+        <v>9.776557207107544</v>
       </c>
       <c r="H21" t="n">
-        <v>7.789126634597778</v>
+        <v>8.490996599197388</v>
       </c>
       <c r="I21" t="n">
-        <v>10.06332635879517</v>
+        <v>7.588284015655518</v>
       </c>
       <c r="J21" t="n">
-        <v>7.112356424331665</v>
+        <v>8.360747814178467</v>
       </c>
       <c r="K21" t="n">
-        <v>7.267966985702515</v>
+        <v>7.642610311508179</v>
       </c>
       <c r="L21" t="n">
-        <v>8.05001666545868</v>
+        <v>8.226452732086182</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>6.69745659828186</v>
+        <v>6.758881568908691</v>
       </c>
       <c r="C22" t="n">
-        <v>5.972218990325928</v>
+        <v>5.863246202468872</v>
       </c>
       <c r="D22" t="n">
-        <v>7.512273550033569</v>
+        <v>8.162230968475342</v>
       </c>
       <c r="E22" t="n">
-        <v>6.864979982376099</v>
+        <v>6.792693138122559</v>
       </c>
       <c r="F22" t="n">
-        <v>7.608585596084595</v>
+        <v>6.858526945114136</v>
       </c>
       <c r="G22" t="n">
-        <v>7.816062450408936</v>
+        <v>6.925829648971558</v>
       </c>
       <c r="H22" t="n">
-        <v>6.240104198455811</v>
+        <v>5.935399770736694</v>
       </c>
       <c r="I22" t="n">
-        <v>6.315417528152466</v>
+        <v>7.050035953521729</v>
       </c>
       <c r="J22" t="n">
-        <v>8.633984327316284</v>
+        <v>8.459923982620239</v>
       </c>
       <c r="K22" t="n">
-        <v>6.943804979324341</v>
+        <v>6.7593092918396</v>
       </c>
       <c r="L22" t="n">
-        <v>7.060488820075989</v>
+        <v>6.956607747077942</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>9.533198356628418</v>
+        <v>9.151703119277954</v>
       </c>
       <c r="C23" t="n">
-        <v>9.48381519317627</v>
+        <v>7.74679160118103</v>
       </c>
       <c r="D23" t="n">
-        <v>8.492839097976685</v>
+        <v>8.755305290222168</v>
       </c>
       <c r="E23" t="n">
-        <v>9.152168035507202</v>
+        <v>8.748686790466309</v>
       </c>
       <c r="F23" t="n">
-        <v>8.902793884277344</v>
+        <v>9.285305023193359</v>
       </c>
       <c r="G23" t="n">
-        <v>9.671855449676514</v>
+        <v>11.69570183753967</v>
       </c>
       <c r="H23" t="n">
-        <v>7.515316486358643</v>
+        <v>8.315973997116089</v>
       </c>
       <c r="I23" t="n">
-        <v>8.561664819717407</v>
+        <v>9.741125822067261</v>
       </c>
       <c r="J23" t="n">
-        <v>10.85931754112244</v>
+        <v>9.137722492218018</v>
       </c>
       <c r="K23" t="n">
-        <v>7.29890513420105</v>
+        <v>7.492005348205566</v>
       </c>
       <c r="L23" t="n">
-        <v>8.947187399864196</v>
+        <v>9.007032132148742</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>8.997556686401367</v>
+        <v>7.268605709075928</v>
       </c>
       <c r="C24" t="n">
-        <v>9.798997402191162</v>
+        <v>9.200528621673584</v>
       </c>
       <c r="D24" t="n">
-        <v>8.997075796127319</v>
+        <v>9.192060947418213</v>
       </c>
       <c r="E24" t="n">
-        <v>9.503281354904175</v>
+        <v>8.833986520767212</v>
       </c>
       <c r="F24" t="n">
-        <v>7.615555763244629</v>
+        <v>9.173171520233154</v>
       </c>
       <c r="G24" t="n">
-        <v>8.349189519882202</v>
+        <v>8.510367393493652</v>
       </c>
       <c r="H24" t="n">
-        <v>7.794130563735962</v>
+        <v>7.57977294921875</v>
       </c>
       <c r="I24" t="n">
-        <v>8.686852931976318</v>
+        <v>7.549352169036865</v>
       </c>
       <c r="J24" t="n">
-        <v>9.554636716842651</v>
+        <v>9.317990064620972</v>
       </c>
       <c r="K24" t="n">
-        <v>8.183670043945312</v>
+        <v>8.516801834106445</v>
       </c>
       <c r="L24" t="n">
-        <v>8.74809467792511</v>
+        <v>8.514263772964478</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>8.783117055892944</v>
+        <v>6.675996065139771</v>
       </c>
       <c r="C25" t="n">
-        <v>7.877463579177856</v>
+        <v>8.852932214736938</v>
       </c>
       <c r="D25" t="n">
-        <v>7.55729866027832</v>
+        <v>6.503925323486328</v>
       </c>
       <c r="E25" t="n">
-        <v>7.870480537414551</v>
+        <v>6.741361618041992</v>
       </c>
       <c r="F25" t="n">
-        <v>7.333802700042725</v>
+        <v>8.502917051315308</v>
       </c>
       <c r="G25" t="n">
-        <v>7.591543674468994</v>
+        <v>7.382668972015381</v>
       </c>
       <c r="H25" t="n">
-        <v>7.284423112869263</v>
+        <v>6.714399337768555</v>
       </c>
       <c r="I25" t="n">
-        <v>6.876019477844238</v>
+        <v>8.002627611160278</v>
       </c>
       <c r="J25" t="n">
-        <v>7.109369277954102</v>
+        <v>7.835045337677002</v>
       </c>
       <c r="K25" t="n">
-        <v>8.831490993499756</v>
+        <v>7.004154920578003</v>
       </c>
       <c r="L25" t="n">
-        <v>7.711500906944275</v>
+        <v>7.421602845191956</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>6.837103605270386</v>
+        <v>7.130333662033081</v>
       </c>
       <c r="C26" t="n">
-        <v>6.706037521362305</v>
+        <v>8.639015197753906</v>
       </c>
       <c r="D26" t="n">
-        <v>8.738742828369141</v>
+        <v>6.83257794380188</v>
       </c>
       <c r="E26" t="n">
-        <v>6.93294882774353</v>
+        <v>9.27386212348938</v>
       </c>
       <c r="F26" t="n">
-        <v>7.276037931442261</v>
+        <v>6.80816125869751</v>
       </c>
       <c r="G26" t="n">
-        <v>6.985852479934692</v>
+        <v>6.865029811859131</v>
       </c>
       <c r="H26" t="n">
-        <v>8.765678882598877</v>
+        <v>8.528797388076782</v>
       </c>
       <c r="I26" t="n">
-        <v>9.63591480255127</v>
+        <v>8.222042322158813</v>
       </c>
       <c r="J26" t="n">
-        <v>8.394159078598022</v>
+        <v>6.930834293365479</v>
       </c>
       <c r="K26" t="n">
-        <v>6.939461231231689</v>
+        <v>8.4889075756073</v>
       </c>
       <c r="L26" t="n">
-        <v>7.721193718910217</v>
+        <v>7.771956157684326</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>10.36720418930054</v>
+        <v>7.389060974121094</v>
       </c>
       <c r="C27" t="n">
-        <v>7.563713550567627</v>
+        <v>9.081387042999268</v>
       </c>
       <c r="D27" t="n">
-        <v>10.91470742225647</v>
+        <v>8.46158504486084</v>
       </c>
       <c r="E27" t="n">
-        <v>10.17254996299744</v>
+        <v>9.638433456420898</v>
       </c>
       <c r="F27" t="n">
-        <v>10.09975719451904</v>
+        <v>10.1925995349884</v>
       </c>
       <c r="G27" t="n">
-        <v>9.416001319885254</v>
+        <v>9.306877374649048</v>
       </c>
       <c r="H27" t="n">
-        <v>10.11269450187683</v>
+        <v>9.686508417129517</v>
       </c>
       <c r="I27" t="n">
-        <v>9.258366584777832</v>
+        <v>9.805495500564575</v>
       </c>
       <c r="J27" t="n">
-        <v>9.497287750244141</v>
+        <v>7.19631028175354</v>
       </c>
       <c r="K27" t="n">
-        <v>9.202507972717285</v>
+        <v>7.596725463867188</v>
       </c>
       <c r="L27" t="n">
-        <v>9.660479044914245</v>
+        <v>8.835498309135437</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>7.610613822937012</v>
+        <v>7.920894861221313</v>
       </c>
       <c r="C28" t="n">
-        <v>7.77673602104187</v>
+        <v>7.890444040298462</v>
       </c>
       <c r="D28" t="n">
-        <v>8.586144208908081</v>
+        <v>9.623958349227905</v>
       </c>
       <c r="E28" t="n">
-        <v>9.991014719009399</v>
+        <v>9.033496379852295</v>
       </c>
       <c r="F28" t="n">
-        <v>7.955702304840088</v>
+        <v>9.400531768798828</v>
       </c>
       <c r="G28" t="n">
-        <v>7.357741594314575</v>
+        <v>8.138303995132446</v>
       </c>
       <c r="H28" t="n">
-        <v>9.807980060577393</v>
+        <v>8.747281551361084</v>
       </c>
       <c r="I28" t="n">
-        <v>7.2076256275177</v>
+        <v>7.877492904663086</v>
       </c>
       <c r="J28" t="n">
-        <v>9.018524408340454</v>
+        <v>8.258003711700439</v>
       </c>
       <c r="K28" t="n">
-        <v>8.034075260162354</v>
+        <v>8.617573738098145</v>
       </c>
       <c r="L28" t="n">
-        <v>8.334615802764892</v>
+        <v>8.5507981300354</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>8.476438045501709</v>
+        <v>9.237989187240601</v>
       </c>
       <c r="C29" t="n">
-        <v>10.16302609443665</v>
+        <v>10.10418844223022</v>
       </c>
       <c r="D29" t="n">
-        <v>11.49207234382629</v>
+        <v>9.71121072769165</v>
       </c>
       <c r="E29" t="n">
-        <v>8.65592360496521</v>
+        <v>7.672717094421387</v>
       </c>
       <c r="F29" t="n">
-        <v>10.8484058380127</v>
+        <v>9.188620567321777</v>
       </c>
       <c r="G29" t="n">
-        <v>9.01700496673584</v>
+        <v>8.02114725112915</v>
       </c>
       <c r="H29" t="n">
-        <v>9.662860631942749</v>
+        <v>10.85677933692932</v>
       </c>
       <c r="I29" t="n">
-        <v>10.57557153701782</v>
+        <v>10.14764189720154</v>
       </c>
       <c r="J29" t="n">
-        <v>9.262926816940308</v>
+        <v>9.638427019119263</v>
       </c>
       <c r="K29" t="n">
-        <v>11.39341425895691</v>
+        <v>10.16557335853577</v>
       </c>
       <c r="L29" t="n">
-        <v>9.954764413833619</v>
+        <v>9.474429488182068</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>7.616574048995972</v>
+        <v>8.362167119979858</v>
       </c>
       <c r="C30" t="n">
-        <v>9.238958358764648</v>
+        <v>8.61307692527771</v>
       </c>
       <c r="D30" t="n">
-        <v>7.360747575759888</v>
+        <v>9.978641510009766</v>
       </c>
       <c r="E30" t="n">
-        <v>8.185104608535767</v>
+        <v>7.361730575561523</v>
       </c>
       <c r="F30" t="n">
-        <v>9.245384454727173</v>
+        <v>8.467948436737061</v>
       </c>
       <c r="G30" t="n">
-        <v>8.823533773422241</v>
+        <v>9.287339925765991</v>
       </c>
       <c r="H30" t="n">
-        <v>9.573115825653076</v>
+        <v>9.002078056335449</v>
       </c>
       <c r="I30" t="n">
-        <v>9.705719470977783</v>
+        <v>9.933216571807861</v>
       </c>
       <c r="J30" t="n">
-        <v>7.35825252532959</v>
+        <v>9.150166034698486</v>
       </c>
       <c r="K30" t="n">
-        <v>7.484886646270752</v>
+        <v>9.56467342376709</v>
       </c>
       <c r="L30" t="n">
-        <v>8.45922772884369</v>
+        <v>8.97210385799408</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>6.927838802337646</v>
+        <v>8.92577075958252</v>
       </c>
       <c r="C31" t="n">
-        <v>10.82537889480591</v>
+        <v>8.893845796585083</v>
       </c>
       <c r="D31" t="n">
-        <v>9.907219171524048</v>
+        <v>9.429985523223877</v>
       </c>
       <c r="E31" t="n">
-        <v>6.640098810195923</v>
+        <v>9.125258922576904</v>
       </c>
       <c r="F31" t="n">
-        <v>10.88723802566528</v>
+        <v>8.450965166091919</v>
       </c>
       <c r="G31" t="n">
-        <v>7.651025056838989</v>
+        <v>6.932828903198242</v>
       </c>
       <c r="H31" t="n">
-        <v>9.664362668991089</v>
+        <v>10.09828162193298</v>
       </c>
       <c r="I31" t="n">
-        <v>7.185702800750732</v>
+        <v>8.512809038162231</v>
       </c>
       <c r="J31" t="n">
-        <v>10.41048073768616</v>
+        <v>10.11771655082703</v>
       </c>
       <c r="K31" t="n">
-        <v>8.886956691741943</v>
+        <v>8.608711004257202</v>
       </c>
       <c r="L31" t="n">
-        <v>8.898630166053772</v>
+        <v>8.909617328643799</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>6.543355703353882</v>
+        <v>6.624292135238647</v>
       </c>
       <c r="C32" t="n">
-        <v>9.546138525009155</v>
+        <v>7.956765174865723</v>
       </c>
       <c r="D32" t="n">
-        <v>8.214061975479126</v>
+        <v>6.627734184265137</v>
       </c>
       <c r="E32" t="n">
-        <v>8.956679582595825</v>
+        <v>11.06882357597351</v>
       </c>
       <c r="F32" t="n">
-        <v>7.006129503250122</v>
+        <v>7.080481052398682</v>
       </c>
       <c r="G32" t="n">
-        <v>7.454547166824341</v>
+        <v>6.854546785354614</v>
       </c>
       <c r="H32" t="n">
-        <v>9.924216270446777</v>
+        <v>8.842493772506714</v>
       </c>
       <c r="I32" t="n">
-        <v>7.232547283172607</v>
+        <v>9.432976245880127</v>
       </c>
       <c r="J32" t="n">
-        <v>7.545278549194336</v>
+        <v>6.638094663619995</v>
       </c>
       <c r="K32" t="n">
-        <v>8.469400405883789</v>
+        <v>10.03938293457031</v>
       </c>
       <c r="L32" t="n">
-        <v>8.089235496520995</v>
+        <v>8.116559052467347</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>10.18150568008423</v>
+        <v>8.924766063690186</v>
       </c>
       <c r="C33" t="n">
-        <v>7.250503063201904</v>
+        <v>8.669883728027344</v>
       </c>
       <c r="D33" t="n">
-        <v>7.235077619552612</v>
+        <v>8.0185866355896</v>
       </c>
       <c r="E33" t="n">
-        <v>7.630655527114868</v>
+        <v>8.347228050231934</v>
       </c>
       <c r="F33" t="n">
-        <v>6.981680154800415</v>
+        <v>8.234107255935669</v>
       </c>
       <c r="G33" t="n">
-        <v>7.91331934928894</v>
+        <v>7.278055429458618</v>
       </c>
       <c r="H33" t="n">
-        <v>8.676408767700195</v>
+        <v>6.925466060638428</v>
       </c>
       <c r="I33" t="n">
-        <v>9.563108682632446</v>
+        <v>6.701056480407715</v>
       </c>
       <c r="J33" t="n">
-        <v>10.81738638877869</v>
+        <v>8.86783766746521</v>
       </c>
       <c r="K33" t="n">
-        <v>7.319859266281128</v>
+        <v>7.420120000839233</v>
       </c>
       <c r="L33" t="n">
-        <v>8.356950449943543</v>
+        <v>7.938710737228393</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>8.973620891571045</v>
+        <v>9.073882341384888</v>
       </c>
       <c r="C34" t="n">
-        <v>7.145309448242188</v>
+        <v>6.176277875900269</v>
       </c>
       <c r="D34" t="n">
-        <v>7.968676328659058</v>
+        <v>8.00959849357605</v>
       </c>
       <c r="E34" t="n">
-        <v>7.814057350158691</v>
+        <v>8.533733367919922</v>
       </c>
       <c r="F34" t="n">
-        <v>6.539822101593018</v>
+        <v>7.590656995773315</v>
       </c>
       <c r="G34" t="n">
-        <v>6.430618762969971</v>
+        <v>8.176687002182007</v>
       </c>
       <c r="H34" t="n">
-        <v>8.996054649353027</v>
+        <v>7.212638378143311</v>
       </c>
       <c r="I34" t="n">
-        <v>6.433580160140991</v>
+        <v>7.930280685424805</v>
       </c>
       <c r="J34" t="n">
-        <v>6.539876222610474</v>
+        <v>8.677380084991455</v>
       </c>
       <c r="K34" t="n">
-        <v>8.19413161277771</v>
+        <v>7.34078574180603</v>
       </c>
       <c r="L34" t="n">
-        <v>7.503574752807618</v>
+        <v>7.872192096710205</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>9.505382061004639</v>
+        <v>7.229092121124268</v>
       </c>
       <c r="C35" t="n">
-        <v>10.40491604804993</v>
+        <v>7.908109426498413</v>
       </c>
       <c r="D35" t="n">
-        <v>8.563212871551514</v>
+        <v>9.485808849334717</v>
       </c>
       <c r="E35" t="n">
-        <v>7.880022525787354</v>
+        <v>8.677021265029907</v>
       </c>
       <c r="F35" t="n">
-        <v>9.487786054611206</v>
+        <v>9.649845361709595</v>
       </c>
       <c r="G35" t="n">
-        <v>9.354128122329712</v>
+        <v>7.465545892715454</v>
       </c>
       <c r="H35" t="n">
-        <v>7.753353357315063</v>
+        <v>10.29071879386902</v>
       </c>
       <c r="I35" t="n">
-        <v>7.368811368942261</v>
+        <v>7.57628345489502</v>
       </c>
       <c r="J35" t="n">
-        <v>7.997178316116333</v>
+        <v>7.333818912506104</v>
       </c>
       <c r="K35" t="n">
-        <v>9.417487382888794</v>
+        <v>7.790148258209229</v>
       </c>
       <c r="L35" t="n">
-        <v>8.77322781085968</v>
+        <v>8.340639233589172</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>7.098044872283936</v>
+        <v>9.543878316879272</v>
       </c>
       <c r="C36" t="n">
-        <v>9.184546709060669</v>
+        <v>9.702294588088989</v>
       </c>
       <c r="D36" t="n">
-        <v>9.825436115264893</v>
+        <v>8.986075401306152</v>
       </c>
       <c r="E36" t="n">
-        <v>10.95353364944458</v>
+        <v>9.822437286376953</v>
       </c>
       <c r="F36" t="n">
-        <v>10.35112738609314</v>
+        <v>10.42086362838745</v>
       </c>
       <c r="G36" t="n">
-        <v>8.940698862075806</v>
+        <v>8.913286447525024</v>
       </c>
       <c r="H36" t="n">
-        <v>9.354694128036499</v>
+        <v>11.34349370002747</v>
       </c>
       <c r="I36" t="n">
-        <v>10.25137042999268</v>
+        <v>9.749118089675903</v>
       </c>
       <c r="J36" t="n">
-        <v>12.51762056350708</v>
+        <v>10.72655248641968</v>
       </c>
       <c r="K36" t="n">
-        <v>8.083387851715088</v>
+        <v>8.626530647277832</v>
       </c>
       <c r="L36" t="n">
-        <v>9.656046056747437</v>
+        <v>9.783453059196471</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>8.732253551483154</v>
+        <v>8.021134853363037</v>
       </c>
       <c r="C37" t="n">
-        <v>6.027655839920044</v>
+        <v>6.277171611785889</v>
       </c>
       <c r="D37" t="n">
-        <v>6.71538257598877</v>
+        <v>6.533485174179077</v>
       </c>
       <c r="E37" t="n">
-        <v>6.508937358856201</v>
+        <v>6.565428733825684</v>
       </c>
       <c r="F37" t="n">
-        <v>6.798715353012085</v>
+        <v>5.994394540786743</v>
       </c>
       <c r="G37" t="n">
-        <v>7.626553058624268</v>
+        <v>8.362257480621338</v>
       </c>
       <c r="H37" t="n">
-        <v>8.736232995986938</v>
+        <v>6.897132873535156</v>
       </c>
       <c r="I37" t="n">
-        <v>6.082021951675415</v>
+        <v>6.354474544525146</v>
       </c>
       <c r="J37" t="n">
-        <v>6.669978618621826</v>
+        <v>6.771870613098145</v>
       </c>
       <c r="K37" t="n">
-        <v>6.374768733978271</v>
+        <v>7.116990804672241</v>
       </c>
       <c r="L37" t="n">
-        <v>7.027250003814697</v>
+        <v>6.889434123039246</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>7.374707698822021</v>
+        <v>8.944207429885864</v>
       </c>
       <c r="C38" t="n">
-        <v>7.806127071380615</v>
+        <v>7.083551406860352</v>
       </c>
       <c r="D38" t="n">
-        <v>8.511809110641479</v>
+        <v>7.214726686477661</v>
       </c>
       <c r="E38" t="n">
-        <v>7.623546123504639</v>
+        <v>7.866451025009155</v>
       </c>
       <c r="F38" t="n">
-        <v>7.150777816772461</v>
+        <v>7.401150941848755</v>
       </c>
       <c r="G38" t="n">
-        <v>7.714815855026245</v>
+        <v>7.190678834915161</v>
       </c>
       <c r="H38" t="n">
-        <v>8.3871169090271</v>
+        <v>8.026569366455078</v>
       </c>
       <c r="I38" t="n">
-        <v>7.481022357940674</v>
+        <v>8.185604333877563</v>
       </c>
       <c r="J38" t="n">
-        <v>8.792639017105103</v>
+        <v>7.463496446609497</v>
       </c>
       <c r="K38" t="n">
-        <v>9.314255952835083</v>
+        <v>9.640437841415405</v>
       </c>
       <c r="L38" t="n">
-        <v>8.015681791305543</v>
+        <v>7.901687431335449</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>6.865110635757446</v>
+        <v>7.986632823944092</v>
       </c>
       <c r="C39" t="n">
-        <v>6.422295093536377</v>
+        <v>7.500871419906616</v>
       </c>
       <c r="D39" t="n">
-        <v>6.809281826019287</v>
+        <v>6.705407381057739</v>
       </c>
       <c r="E39" t="n">
-        <v>9.085839748382568</v>
+        <v>7.522301912307739</v>
       </c>
       <c r="F39" t="n">
-        <v>7.418684720993042</v>
+        <v>6.979193449020386</v>
       </c>
       <c r="G39" t="n">
-        <v>6.735941410064697</v>
+        <v>8.069934129714966</v>
       </c>
       <c r="H39" t="n">
-        <v>6.834200859069824</v>
+        <v>6.670989990234375</v>
       </c>
       <c r="I39" t="n">
-        <v>9.019516944885254</v>
+        <v>8.82850980758667</v>
       </c>
       <c r="J39" t="n">
-        <v>6.545464754104614</v>
+        <v>7.451498985290527</v>
       </c>
       <c r="K39" t="n">
-        <v>8.926297187805176</v>
+        <v>7.28743314743042</v>
       </c>
       <c r="L39" t="n">
-        <v>7.466263318061829</v>
+        <v>7.500277304649353</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>7.407715082168579</v>
+        <v>7.800637245178223</v>
       </c>
       <c r="C40" t="n">
-        <v>8.703320026397705</v>
+        <v>8.950174331665039</v>
       </c>
       <c r="D40" t="n">
-        <v>7.046189308166504</v>
+        <v>8.495329618453979</v>
       </c>
       <c r="E40" t="n">
-        <v>7.387236356735229</v>
+        <v>7.23608922958374</v>
       </c>
       <c r="F40" t="n">
-        <v>9.037960290908813</v>
+        <v>9.31973671913147</v>
       </c>
       <c r="G40" t="n">
-        <v>8.639523267745972</v>
+        <v>7.744758367538452</v>
       </c>
       <c r="H40" t="n">
-        <v>7.099999666213989</v>
+        <v>9.131214618682861</v>
       </c>
       <c r="I40" t="n">
-        <v>8.567221403121948</v>
+        <v>7.918325662612915</v>
       </c>
       <c r="J40" t="n">
-        <v>7.969278335571289</v>
+        <v>8.712279558181763</v>
       </c>
       <c r="K40" t="n">
-        <v>7.330225944519043</v>
+        <v>9.183564424514771</v>
       </c>
       <c r="L40" t="n">
-        <v>7.918866968154907</v>
+        <v>8.449210977554321</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>11.40192341804504</v>
+        <v>9.512263059616089</v>
       </c>
       <c r="C41" t="n">
-        <v>10.01843333244324</v>
+        <v>7.726816415786743</v>
       </c>
       <c r="D41" t="n">
-        <v>8.763130187988281</v>
+        <v>10.15864109992981</v>
       </c>
       <c r="E41" t="n">
-        <v>8.833496570587158</v>
+        <v>9.681284189224243</v>
       </c>
       <c r="F41" t="n">
-        <v>7.341798305511475</v>
+        <v>8.325870275497437</v>
       </c>
       <c r="G41" t="n">
-        <v>10.38751316070557</v>
+        <v>7.826631307601929</v>
       </c>
       <c r="H41" t="n">
-        <v>7.893407821655273</v>
+        <v>10.86555457115173</v>
       </c>
       <c r="I41" t="n">
-        <v>12.35100269317627</v>
+        <v>7.600634336471558</v>
       </c>
       <c r="J41" t="n">
-        <v>10.23689389228821</v>
+        <v>11.19748425483704</v>
       </c>
       <c r="K41" t="n">
-        <v>9.266870737075806</v>
+        <v>8.011595249176025</v>
       </c>
       <c r="L41" t="n">
-        <v>9.649447011947633</v>
+        <v>9.09067747592926</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>7.003155469894409</v>
+        <v>6.98419451713562</v>
       </c>
       <c r="C42" t="n">
-        <v>7.653456211090088</v>
+        <v>5.793228149414062</v>
       </c>
       <c r="D42" t="n">
-        <v>6.055570602416992</v>
+        <v>6.047577857971191</v>
       </c>
       <c r="E42" t="n">
-        <v>6.915889978408813</v>
+        <v>6.3064284324646</v>
       </c>
       <c r="F42" t="n">
-        <v>6.169306755065918</v>
+        <v>5.619683980941772</v>
       </c>
       <c r="G42" t="n">
-        <v>7.925286769866943</v>
+        <v>8.371181964874268</v>
       </c>
       <c r="H42" t="n">
-        <v>5.969299554824829</v>
+        <v>6.244580745697021</v>
       </c>
       <c r="I42" t="n">
-        <v>5.903454065322876</v>
+        <v>6.311427116394043</v>
       </c>
       <c r="J42" t="n">
-        <v>7.932332992553711</v>
+        <v>5.999722480773926</v>
       </c>
       <c r="K42" t="n">
-        <v>6.455060243606567</v>
+        <v>6.072510957717896</v>
       </c>
       <c r="L42" t="n">
-        <v>6.798281264305115</v>
+        <v>6.37505362033844</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>6.840575933456421</v>
+        <v>8.279886722564697</v>
       </c>
       <c r="C43" t="n">
-        <v>8.782597064971924</v>
+        <v>8.520777463912964</v>
       </c>
       <c r="D43" t="n">
-        <v>6.872976064682007</v>
+        <v>7.879406690597534</v>
       </c>
       <c r="E43" t="n">
-        <v>7.817348003387451</v>
+        <v>7.796144008636475</v>
       </c>
       <c r="F43" t="n">
-        <v>7.184273719787598</v>
+        <v>8.273892164230347</v>
       </c>
       <c r="G43" t="n">
-        <v>10.20547437667847</v>
+        <v>8.688371896743774</v>
       </c>
       <c r="H43" t="n">
-        <v>8.169244766235352</v>
+        <v>7.160227060317993</v>
       </c>
       <c r="I43" t="n">
-        <v>8.773650169372559</v>
+        <v>7.662988901138306</v>
       </c>
       <c r="J43" t="n">
-        <v>7.748709440231323</v>
+        <v>7.856977939605713</v>
       </c>
       <c r="K43" t="n">
-        <v>6.422621011734009</v>
+        <v>6.552793502807617</v>
       </c>
       <c r="L43" t="n">
-        <v>7.881747055053711</v>
+        <v>7.867146635055542</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>6.52185583114624</v>
+        <v>7.234563112258911</v>
       </c>
       <c r="C44" t="n">
-        <v>8.255928993225098</v>
+        <v>7.483448505401611</v>
       </c>
       <c r="D44" t="n">
-        <v>7.483415842056274</v>
+        <v>7.016140222549438</v>
       </c>
       <c r="E44" t="n">
-        <v>8.193568706512451</v>
+        <v>8.224051237106323</v>
       </c>
       <c r="F44" t="n">
-        <v>7.697907686233521</v>
+        <v>7.397637605667114</v>
       </c>
       <c r="G44" t="n">
-        <v>7.333791017532349</v>
+        <v>6.738872528076172</v>
       </c>
       <c r="H44" t="n">
-        <v>8.828486680984497</v>
+        <v>7.141331195831299</v>
       </c>
       <c r="I44" t="n">
-        <v>6.906920671463013</v>
+        <v>6.991192102432251</v>
       </c>
       <c r="J44" t="n">
-        <v>7.236436128616333</v>
+        <v>6.37125825881958</v>
       </c>
       <c r="K44" t="n">
-        <v>9.57206392288208</v>
+        <v>8.257434368133545</v>
       </c>
       <c r="L44" t="n">
-        <v>7.803037548065186</v>
+        <v>7.285592913627625</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>8.924275159835815</v>
+        <v>8.338229894638062</v>
       </c>
       <c r="C45" t="n">
-        <v>9.884783029556274</v>
+        <v>9.182620286941528</v>
       </c>
       <c r="D45" t="n">
-        <v>10.43982720375061</v>
+        <v>7.447021722793579</v>
       </c>
       <c r="E45" t="n">
-        <v>10.58939576148987</v>
+        <v>9.012030124664307</v>
       </c>
       <c r="F45" t="n">
-        <v>9.499232769012451</v>
+        <v>9.022638559341431</v>
       </c>
       <c r="G45" t="n">
-        <v>10.11813759803772</v>
+        <v>8.536279439926147</v>
       </c>
       <c r="H45" t="n">
-        <v>8.764182567596436</v>
+        <v>8.398142337799072</v>
       </c>
       <c r="I45" t="n">
-        <v>8.336824178695679</v>
+        <v>9.127289772033691</v>
       </c>
       <c r="J45" t="n">
-        <v>7.428687572479248</v>
+        <v>7.380203723907471</v>
       </c>
       <c r="K45" t="n">
-        <v>7.143883943557739</v>
+        <v>9.71523642539978</v>
       </c>
       <c r="L45" t="n">
-        <v>9.112922978401183</v>
+        <v>8.615969228744508</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>7.610159873962402</v>
+        <v>8.004638433456421</v>
       </c>
       <c r="C46" t="n">
-        <v>7.264070510864258</v>
+        <v>9.747647762298584</v>
       </c>
       <c r="D46" t="n">
-        <v>7.017720222473145</v>
+        <v>8.219053268432617</v>
       </c>
       <c r="E46" t="n">
-        <v>7.862032651901245</v>
+        <v>6.993167161941528</v>
       </c>
       <c r="F46" t="n">
-        <v>6.895023822784424</v>
+        <v>8.355195760726929</v>
       </c>
       <c r="G46" t="n">
-        <v>9.284349203109741</v>
+        <v>7.547292232513428</v>
       </c>
       <c r="H46" t="n">
-        <v>7.312458753585815</v>
+        <v>7.577685356140137</v>
       </c>
       <c r="I46" t="n">
-        <v>8.151247501373291</v>
+        <v>8.983117580413818</v>
       </c>
       <c r="J46" t="n">
-        <v>7.368076324462891</v>
+        <v>8.621018171310425</v>
       </c>
       <c r="K46" t="n">
-        <v>9.345678567886353</v>
+        <v>8.512831449508667</v>
       </c>
       <c r="L46" t="n">
-        <v>7.811081743240356</v>
+        <v>8.256164717674256</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>8.827540159225464</v>
+        <v>7.698884248733521</v>
       </c>
       <c r="C47" t="n">
-        <v>9.222471237182617</v>
+        <v>7.320840358734131</v>
       </c>
       <c r="D47" t="n">
-        <v>7.352025270462036</v>
+        <v>8.802731275558472</v>
       </c>
       <c r="E47" t="n">
-        <v>7.620934963226318</v>
+        <v>7.548267126083374</v>
       </c>
       <c r="F47" t="n">
-        <v>9.19606614112854</v>
+        <v>8.967623233795166</v>
       </c>
       <c r="G47" t="n">
-        <v>9.120245933532715</v>
+        <v>7.554755926132202</v>
       </c>
       <c r="H47" t="n">
-        <v>9.550658702850342</v>
+        <v>8.973620414733887</v>
       </c>
       <c r="I47" t="n">
-        <v>8.672775030136108</v>
+        <v>8.551230669021606</v>
       </c>
       <c r="J47" t="n">
-        <v>8.175164699554443</v>
+        <v>9.429968357086182</v>
       </c>
       <c r="K47" t="n">
-        <v>7.793623685836792</v>
+        <v>10.04140663146973</v>
       </c>
       <c r="L47" t="n">
-        <v>8.553150582313538</v>
+        <v>8.488932824134826</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>7.016123294830322</v>
+        <v>7.634537935256958</v>
       </c>
       <c r="C48" t="n">
-        <v>7.470442056655884</v>
+        <v>9.17210841178894</v>
       </c>
       <c r="D48" t="n">
-        <v>9.133222103118896</v>
+        <v>10.57503986358643</v>
       </c>
       <c r="E48" t="n">
-        <v>9.414989948272705</v>
+        <v>8.47365927696228</v>
       </c>
       <c r="F48" t="n">
-        <v>8.585125923156738</v>
+        <v>8.16971492767334</v>
       </c>
       <c r="G48" t="n">
-        <v>7.616566181182861</v>
+        <v>8.162261724472046</v>
       </c>
       <c r="H48" t="n">
-        <v>8.983563423156738</v>
+        <v>7.003793239593506</v>
       </c>
       <c r="I48" t="n">
-        <v>7.560744047164917</v>
+        <v>6.886513471603394</v>
       </c>
       <c r="J48" t="n">
-        <v>7.497877597808838</v>
+        <v>8.144757032394409</v>
       </c>
       <c r="K48" t="n">
-        <v>7.025081634521484</v>
+        <v>9.207617044448853</v>
       </c>
       <c r="L48" t="n">
-        <v>8.030373620986939</v>
+        <v>8.343000292778015</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>7.601619482040405</v>
+        <v>9.813078641891479</v>
       </c>
       <c r="C49" t="n">
-        <v>8.681855201721191</v>
+        <v>7.666040182113647</v>
       </c>
       <c r="D49" t="n">
-        <v>7.62755298614502</v>
+        <v>8.061553001403809</v>
       </c>
       <c r="E49" t="n">
-        <v>7.688891649246216</v>
+        <v>7.855593204498291</v>
       </c>
       <c r="F49" t="n">
-        <v>7.711836099624634</v>
+        <v>8.220685720443726</v>
       </c>
       <c r="G49" t="n">
-        <v>8.264947652816772</v>
+        <v>9.370198011398315</v>
       </c>
       <c r="H49" t="n">
-        <v>7.994632005691528</v>
+        <v>7.622565507888794</v>
       </c>
       <c r="I49" t="n">
-        <v>9.573604822158813</v>
+        <v>8.107870817184448</v>
       </c>
       <c r="J49" t="n">
-        <v>8.315785884857178</v>
+        <v>8.210555553436279</v>
       </c>
       <c r="K49" t="n">
-        <v>7.473443031311035</v>
+        <v>8.169166564941406</v>
       </c>
       <c r="L49" t="n">
-        <v>8.093416881561279</v>
+        <v>8.309730720520019</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>10.34970736503601</v>
+        <v>9.011070013046265</v>
       </c>
       <c r="C50" t="n">
-        <v>12.69962811470032</v>
+        <v>8.562219381332397</v>
       </c>
       <c r="D50" t="n">
-        <v>9.809014320373535</v>
+        <v>10.19620323181152</v>
       </c>
       <c r="E50" t="n">
-        <v>9.957123279571533</v>
+        <v>6.770373344421387</v>
       </c>
       <c r="F50" t="n">
-        <v>9.553191661834717</v>
+        <v>9.491792917251587</v>
       </c>
       <c r="G50" t="n">
-        <v>10.07374668121338</v>
+        <v>8.873892784118652</v>
       </c>
       <c r="H50" t="n">
-        <v>9.889754295349121</v>
+        <v>10.81384491920471</v>
       </c>
       <c r="I50" t="n">
-        <v>10.52408719062805</v>
+        <v>9.473394870758057</v>
       </c>
       <c r="J50" t="n">
-        <v>8.879502058029175</v>
+        <v>9.378106117248535</v>
       </c>
       <c r="K50" t="n">
-        <v>10.44732999801636</v>
+        <v>10.59583640098572</v>
       </c>
       <c r="L50" t="n">
-        <v>10.21830849647522</v>
+        <v>9.316673398017883</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>7.207607269287109</v>
+        <v>8.68990421295166</v>
       </c>
       <c r="C51" t="n">
-        <v>7.304373025894165</v>
+        <v>9.02801251411438</v>
       </c>
       <c r="D51" t="n">
-        <v>8.837976455688477</v>
+        <v>7.134290456771851</v>
       </c>
       <c r="E51" t="n">
-        <v>8.166689157485962</v>
+        <v>8.583156824111938</v>
       </c>
       <c r="F51" t="n">
-        <v>7.298917055130005</v>
+        <v>7.455010414123535</v>
       </c>
       <c r="G51" t="n">
-        <v>11.18995809555054</v>
+        <v>8.444492101669312</v>
       </c>
       <c r="H51" t="n">
-        <v>7.181719541549683</v>
+        <v>9.156662464141846</v>
       </c>
       <c r="I51" t="n">
-        <v>8.253937959671021</v>
+        <v>7.486929178237915</v>
       </c>
       <c r="J51" t="n">
-        <v>7.306332349777222</v>
+        <v>9.050435066223145</v>
       </c>
       <c r="K51" t="n">
-        <v>7.930853843688965</v>
+        <v>8.848718166351318</v>
       </c>
       <c r="L51" t="n">
-        <v>8.067836475372314</v>
+        <v>8.38776113986969</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8.008850016593932</v>
+        <v>8.04856722354889</v>
       </c>
       <c r="C52" t="n">
-        <v>8.280859661102294</v>
+        <v>7.933749895095826</v>
       </c>
       <c r="D52" t="n">
-        <v>8.154672441482544</v>
+        <v>8.157738676071167</v>
       </c>
       <c r="E52" t="n">
-        <v>8.202723722457886</v>
+        <v>8.058286914825439</v>
       </c>
       <c r="F52" t="n">
-        <v>7.919529962539673</v>
+        <v>8.379077920913696</v>
       </c>
       <c r="G52" t="n">
-        <v>8.217337660789489</v>
+        <v>8.187724103927613</v>
       </c>
       <c r="H52" t="n">
-        <v>8.188125782012939</v>
+        <v>8.187352447509765</v>
       </c>
       <c r="I52" t="n">
-        <v>8.113857531547547</v>
+        <v>8.214495444297791</v>
       </c>
       <c r="J52" t="n">
-        <v>8.191225385665893</v>
+        <v>8.059308729171754</v>
       </c>
       <c r="K52" t="n">
-        <v>8.292059621810914</v>
+        <v>8.280834279060365</v>
       </c>
       <c r="L52" t="n">
-        <v>8.156924178600311</v>
+        <v>8.150713563442229</v>
       </c>
     </row>
   </sheetData>
